--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-17 - 2026-08-23).xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-17 - 2026-08-23).xlsx
@@ -731,12 +731,6 @@
     <t>FORTALEZA</t>
   </si>
   <si>
-    <t>VARGINHA</t>
-  </si>
-  <si>
-    <t>Poloni,Gabriel Godoy</t>
-  </si>
-  <si>
     <t>ARMACAO DOS BUZIOS</t>
   </si>
   <si>
@@ -887,34 +881,34 @@
     <t>BELO HORIZONTE</t>
   </si>
   <si>
-    <t>187
-165</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>R$ 6.694.171,66</t>
-  </si>
-  <si>
-    <t>R$ 40.711,73
-R$ 39.320,09</t>
-  </si>
-  <si>
-    <t>7.2%
-7.5%</t>
-  </si>
-  <si>
-    <t>434.9</t>
-  </si>
-  <si>
-    <t>(8.8%)</t>
-  </si>
-  <si>
-    <t>28.2%</t>
-  </si>
-  <si>
-    <t>(9.9%)</t>
+    <t>186
+168</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>R$ 7.128.122,78</t>
+  </si>
+  <si>
+    <t>R$ 41.408,18
+R$ 41.505,94</t>
+  </si>
+  <si>
+    <t>9.6%
+10.0%</t>
+  </si>
+  <si>
+    <t>442.0</t>
+  </si>
+  <si>
+    <t>(8.6%)</t>
+  </si>
+  <si>
+    <t>28.4%</t>
+  </si>
+  <si>
+    <t>(9.5%)</t>
   </si>
   <si>
     <t>3.1%</t>
@@ -923,34 +917,34 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>28.0</t>
-  </si>
-  <si>
-    <t>66.0%</t>
-  </si>
-  <si>
-    <t>12.0%</t>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>65.7%</t>
+  </si>
+  <si>
+    <t>12.1%</t>
   </si>
   <si>
     <t>5.6</t>
   </si>
   <si>
-    <t>7.2</t>
+    <t>7.3</t>
   </si>
   <si>
     <t>12.9</t>
   </si>
   <si>
-    <t>19.6</t>
-  </si>
-  <si>
-    <t>67.6%</t>
-  </si>
-  <si>
-    <t>-R$ 199.253,76</t>
-  </si>
-  <si>
-    <t>2.74</t>
+    <t>19.7</t>
+  </si>
+  <si>
+    <t>67.2%</t>
+  </si>
+  <si>
+    <t>-R$ 243.025,60</t>
+  </si>
+  <si>
+    <t>2.76</t>
   </si>
   <si>
     <t>3.14</t>
@@ -1372,7 +1366,7 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="5.43" customWidth="1"/>
-    <col min="2" max="2" width="3.57" customWidth="1"/>
+    <col min="2" max="2" width="3.14" customWidth="1"/>
     <col min="3" max="3" width="17.86" customWidth="1"/>
     <col min="4" max="4" width="4.43" customWidth="1"/>
     <col min="5" max="5" width="26.57" customWidth="1"/>
@@ -2082,7 +2076,7 @@
         <v>19521</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2122,22 +2116,22 @@
         <v>76943.570000000007</v>
       </c>
       <c r="P6" s="5">
-        <v>89767.498333333337</v>
+        <v>76943.569999999992</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.60772349059863595</v>
+        <v>0.37804870622740228</v>
       </c>
       <c r="R6" s="7">
-        <v>926.33333333333337</v>
+        <v>794</v>
       </c>
       <c r="S6" s="6">
         <v>0.14905933429811857</v>
       </c>
       <c r="T6" s="6">
-        <v>0.0016219678915340163</v>
+        <v>0.0018562694712501641</v>
       </c>
       <c r="U6" s="6">
-        <v>-0.37337219991222137</v>
+        <v>-0.37313789833250521</v>
       </c>
       <c r="V6" s="6">
         <v>0.036521167395794085</v>
@@ -2868,7 +2862,7 @@
         <v>19536</v>
       </c>
       <c r="B12" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C12" s="4">
         <v>44</v>
@@ -2905,59 +2899,59 @@
         <v>52</v>
       </c>
       <c r="O12" s="5">
-        <v>11397.639999999999</v>
+        <v>48162.82</v>
       </c>
       <c r="P12" s="5">
-        <v>26594.493333333332</v>
+        <v>48162.82</v>
       </c>
       <c r="Q12" s="6">
-        <v>-0.31312184814335753</v>
+        <v>0.24394130676441317</v>
       </c>
       <c r="R12" s="7">
-        <v>301</v>
+        <v>545</v>
       </c>
       <c r="S12" s="6">
-        <v>-0.14000000000000001</v>
+        <v>0.024436090225563811</v>
       </c>
       <c r="T12" s="6">
-        <v>-2.0707094451131987</v>
+        <v>0.33684826386827016</v>
       </c>
       <c r="U12" s="6">
-        <v>-2.3666794880343649</v>
+        <v>0.0060044719142276137</v>
       </c>
       <c r="V12" s="6">
-        <v>0.038332189821752578</v>
+        <v>0.023648532208039315</v>
       </c>
       <c r="W12" s="6">
-        <v>0.015874909191727411</v>
+        <v>0.0042165305104642963</v>
       </c>
       <c r="X12" s="8">
-        <v>30.853431372549021</v>
+        <v>30.438809285714285</v>
       </c>
       <c r="Y12" s="6">
-        <v>0.74509803921568629</v>
+        <v>0.62380952380952381</v>
       </c>
       <c r="Z12" s="6">
-        <v>0.16666666666666666</v>
+        <v>0.12619047619047619</v>
       </c>
       <c r="AA12" s="8">
-        <v>5.5674484375000004</v>
+        <v>5.7598402214022144</v>
       </c>
       <c r="AB12" s="8">
-        <v>9.1567653465346535</v>
+        <v>8.1346522781774588</v>
       </c>
       <c r="AC12" s="8">
         <v>14.799713000000001</v>
       </c>
       <c r="AD12" s="8">
-        <v>21.591012745098041</v>
+        <v>20.798928333333333</v>
       </c>
       <c r="AE12" s="6">
-        <v>0.5</v>
+        <v>0.48809523809523808</v>
       </c>
       <c r="AF12" s="9"/>
       <c r="AG12" s="5">
-        <v>-167.59999999999999</v>
+        <v>-1315.8399999999999</v>
       </c>
       <c r="AH12" s="10">
         <v>2</v>
@@ -3261,7 +3255,7 @@
         <v>19545</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>44</v>
@@ -3298,59 +3292,59 @@
         <v>52</v>
       </c>
       <c r="O15" s="5">
-        <v>31657.429999999997</v>
+        <v>40002.579999999994</v>
       </c>
       <c r="P15" s="5">
-        <v>36933.668333333328</v>
+        <v>40002.579999999994</v>
       </c>
       <c r="Q15" s="6">
-        <v>-0.34151707859213598</v>
+        <v>-0.28680207163504179</v>
       </c>
       <c r="R15" s="7">
-        <v>344.16666666666663</v>
+        <v>378</v>
       </c>
       <c r="S15" s="6">
-        <v>-0.47415329768270953</v>
+        <v>-0.46153846153846156</v>
       </c>
       <c r="T15" s="6">
-        <v>0.22613372595311748</v>
+        <v>0.23776019946713434</v>
       </c>
       <c r="U15" s="6">
-        <v>-0.19113008857636263</v>
+        <v>-0.18223021115138074</v>
       </c>
       <c r="V15" s="6">
-        <v>0.018237235303055242</v>
+        <v>0.022912559639903227</v>
       </c>
       <c r="W15" s="6">
-        <v>0.0074789393832664242</v>
+        <v>0.012364489990395619</v>
       </c>
       <c r="X15" s="8">
-        <v>24.896252071005915</v>
+        <v>29.221836111111109</v>
       </c>
       <c r="Y15" s="6">
-        <v>0.52352941176470591</v>
+        <v>0.48847926267281105</v>
       </c>
       <c r="Z15" s="6">
-        <v>0.059171597633136092</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="AA15" s="8">
-        <v>5.3594824137931036</v>
+        <v>6.8273455764075068</v>
       </c>
       <c r="AB15" s="8">
-        <v>7.0425248484848479</v>
+        <v>8.7500783018867914</v>
       </c>
       <c r="AC15" s="8">
-        <v>12.798823000000001</v>
+        <v>16.133714999999999</v>
       </c>
       <c r="AD15" s="8">
-        <v>20.485009467455622</v>
+        <v>23.862808333333334</v>
       </c>
       <c r="AE15" s="6">
-        <v>0.79289940828402372</v>
+        <v>0.68981481481481477</v>
       </c>
       <c r="AF15" s="9"/>
       <c r="AG15" s="5">
-        <v>-1447.2</v>
+        <v>-1646.4000000000001</v>
       </c>
       <c r="AH15" s="10">
         <v>2</v>
@@ -3392,7 +3386,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>44</v>
@@ -3429,59 +3423,59 @@
         <v>52</v>
       </c>
       <c r="O16" s="5">
-        <v>34327.729999999996</v>
+        <v>42286.769999999997</v>
       </c>
       <c r="P16" s="5">
-        <v>40049.018333333333</v>
+        <v>42286.769999999997</v>
       </c>
       <c r="Q16" s="6">
-        <v>-0.0020353910264876429</v>
+        <v>0.053726199642667671</v>
       </c>
       <c r="R16" s="7">
-        <v>411.83333333333337</v>
+        <v>436</v>
       </c>
       <c r="S16" s="6">
-        <v>-0.20316027088036104</v>
+        <v>-0.20727272727272728</v>
       </c>
       <c r="T16" s="6">
-        <v>-0.0068410698872311097</v>
+        <v>-0.0048414031149695289</v>
       </c>
       <c r="U16" s="6">
-        <v>-0.32731172145667653</v>
+        <v>-0.32123657824894175</v>
       </c>
       <c r="V16" s="6">
-        <v>0.077158801353890846</v>
+        <v>0.075305184103680659</v>
       </c>
       <c r="W16" s="6">
-        <v>0.06808421354980361</v>
+        <v>0.066564152334169763</v>
       </c>
       <c r="X16" s="8">
-        <v>25.138764044943819</v>
+        <v>25.442074222222221</v>
       </c>
       <c r="Y16" s="6">
-        <v>0.6910112359550562</v>
+        <v>0.63111111111111107</v>
       </c>
       <c r="Z16" s="6">
-        <v>0.061797752808988762</v>
+        <v>0.06222222222222222</v>
       </c>
       <c r="AA16" s="8">
-        <v>3.5175141242937853</v>
+        <v>3.5490442660550459</v>
       </c>
       <c r="AB16" s="8">
-        <v>6.9966286516853931</v>
+        <v>7.0522959999999992</v>
       </c>
       <c r="AC16" s="8">
-        <v>10.449313999999999</v>
+        <v>10.646936</v>
       </c>
       <c r="AD16" s="8">
-        <v>17.414232022471911</v>
+        <v>17.607259111111112</v>
       </c>
       <c r="AE16" s="6">
-        <v>0.7528089887640449</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="AF16" s="9"/>
       <c r="AG16" s="5">
-        <v>-7239.5699999999997</v>
+        <v>-8310.7099999999991</v>
       </c>
       <c r="AH16" s="10">
         <v>2</v>
@@ -3862,7 +3856,7 @@
         <v>6.1555007389162562</v>
       </c>
       <c r="AC19" s="8">
-        <v>8.0592760000000006</v>
+        <v>8.9070509999999992</v>
       </c>
       <c r="AD19" s="8">
         <v>16.546141766109788</v>
@@ -4045,7 +4039,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>44</v>
@@ -4080,55 +4074,55 @@
         <v>52</v>
       </c>
       <c r="O21" s="5">
-        <v>41158.07</v>
+        <v>51571.229999999996</v>
       </c>
       <c r="P21" s="5">
-        <v>48017.748333333329</v>
+        <v>51571.229999999996</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.20819488260267094</v>
+        <v>0.29760553833116354</v>
       </c>
       <c r="R21" s="7">
-        <v>446.83333333333337</v>
+        <v>479</v>
       </c>
       <c r="S21" s="6">
-        <v>0.069832402234637048</v>
+        <v>0.052747252747252782</v>
       </c>
       <c r="T21" s="6">
-        <v>0.29473401935513499</v>
+        <v>0.30108936901446792</v>
       </c>
       <c r="U21" s="6">
-        <v>-0.031703784944240587</v>
+        <v>-0.024484405355466605</v>
       </c>
       <c r="V21" s="6">
-        <v>0.023496509918953926</v>
+        <v>0.022810537968553396</v>
       </c>
       <c r="W21" s="6">
-        <v>-0.0066351264770189659</v>
+        <v>-0.0054379641517179247</v>
       </c>
       <c r="X21" s="8">
-        <v>26.970392682926828</v>
+        <v>26.181564630225079</v>
       </c>
       <c r="Y21" s="6">
-        <v>0.84552845528455289</v>
+        <v>0.84565916398713825</v>
       </c>
       <c r="Z21" s="6">
-        <v>0.085365853658536592</v>
+        <v>0.067524115755627015</v>
       </c>
       <c r="AA21" s="8">
-        <v>4.8367948717948712</v>
+        <v>4.6274932377049183</v>
       </c>
       <c r="AB21" s="8">
-        <v>6.1850268292682919</v>
+        <v>5.6709536977491961</v>
       </c>
       <c r="AC21" s="8">
-        <v>10.652098000000001</v>
+        <v>9.9886879999999998</v>
       </c>
       <c r="AD21" s="8">
-        <v>17.614567073170733</v>
+        <v>16.951286816720256</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.73170731707317072</v>
+        <v>0.76527331189710612</v>
       </c>
       <c r="AF21" s="9"/>
       <c r="AG21" s="5">
@@ -4436,7 +4430,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4473,55 +4467,55 @@
         <v>52</v>
       </c>
       <c r="O24" s="5">
-        <v>39383.940000000002</v>
+        <v>52348.610000000001</v>
       </c>
       <c r="P24" s="5">
-        <v>45947.93</v>
+        <v>52348.610000000001</v>
       </c>
       <c r="Q24" s="6">
-        <v>0.013394167659337874</v>
+        <v>0.15456291630707386</v>
       </c>
       <c r="R24" s="7">
-        <v>516.83333333333326</v>
+        <v>594</v>
       </c>
       <c r="S24" s="6">
-        <v>-0.095918367346939037</v>
+        <v>-0.12389380530973448</v>
       </c>
       <c r="T24" s="6">
-        <v>0.26348772367619894</v>
+        <v>0.26726098744551191</v>
       </c>
       <c r="U24" s="6">
-        <v>-0.053163682963157065</v>
+        <v>-0.04857987251237425</v>
       </c>
       <c r="V24" s="6">
-        <v>0.077120115458229915</v>
+        <v>0.068120271006240657</v>
       </c>
       <c r="W24" s="6">
-        <v>0.043067656511765959</v>
+        <v>0.037962450196862917</v>
       </c>
       <c r="X24" s="8">
-        <v>28.244905660377356</v>
+        <v>27.722899445983384</v>
       </c>
       <c r="Y24" s="6">
-        <v>0.96981132075471699</v>
+        <v>0.90027700831024926</v>
       </c>
       <c r="Z24" s="6">
-        <v>0.14339622641509434</v>
+        <v>0.11080332409972299</v>
       </c>
       <c r="AA24" s="8">
-        <v>4.354724036281179</v>
+        <v>3.9588135593220337</v>
       </c>
       <c r="AB24" s="8">
-        <v>8.2245650602409643</v>
+        <v>7.658963372093023</v>
       </c>
       <c r="AC24" s="8">
-        <v>12.627758999999999</v>
+        <v>11.647774999999999</v>
       </c>
       <c r="AD24" s="8">
-        <v>19.788427924528303</v>
+        <v>19.01038808864266</v>
       </c>
       <c r="AE24" s="6">
-        <v>0.67924528301886788</v>
+        <v>0.70083102493074789</v>
       </c>
       <c r="AF24" s="9"/>
       <c r="AG24" s="5">
@@ -4567,7 +4561,7 @@
         <v>19572</v>
       </c>
       <c r="B25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C25" s="4">
         <v>44</v>
@@ -4604,55 +4598,55 @@
         <v>52</v>
       </c>
       <c r="O25" s="5">
-        <v>74192.369999999995</v>
+        <v>92667.660000000003</v>
       </c>
       <c r="P25" s="5">
-        <v>86557.764999999999</v>
+        <v>92667.660000000003</v>
       </c>
       <c r="Q25" s="6">
-        <v>0.13711563224920043</v>
+        <v>0.21738176569085366</v>
       </c>
       <c r="R25" s="7">
-        <v>1010.3333333333334</v>
+        <v>1096</v>
       </c>
       <c r="S25" s="6">
-        <v>0.2371428571428571</v>
+        <v>0.25832376578645233</v>
       </c>
       <c r="T25" s="6">
-        <v>0.30475964711735182</v>
+        <v>0.30811884318650107</v>
       </c>
       <c r="U25" s="6">
-        <v>0.0058063989598930461</v>
+        <v>0.0083587111188520337</v>
       </c>
       <c r="V25" s="6">
-        <v>0.030152413246806922</v>
+        <v>0.029611819268987691</v>
       </c>
       <c r="W25" s="6">
-        <v>0.0077714056041072689</v>
+        <v>0.0079209726456889052</v>
       </c>
       <c r="X25" s="8">
-        <v>28.306058602846051</v>
+        <v>27.871186088709678</v>
       </c>
       <c r="Y25" s="6">
-        <v>0.39974126778783958</v>
+        <v>0.36995967741935482</v>
       </c>
       <c r="Z25" s="6">
-        <v>0.11125485122897801</v>
+        <v>0.10080645161290322</v>
       </c>
       <c r="AA25" s="8">
-        <v>3.6860497089639113</v>
+        <v>3.7195952161913524</v>
       </c>
       <c r="AB25" s="8">
-        <v>6.7964383064516136</v>
+        <v>6.6216615141955835</v>
       </c>
       <c r="AC25" s="8">
-        <v>10.582667000000001</v>
+        <v>10.413150999999999</v>
       </c>
       <c r="AD25" s="8">
-        <v>17.097542173350583</v>
+        <v>16.883619052419355</v>
       </c>
       <c r="AE25" s="6">
-        <v>0.61578266494178524</v>
+        <v>0.63709677419354838</v>
       </c>
       <c r="AF25" s="9"/>
       <c r="AG25" s="5">
@@ -4829,7 +4823,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4866,59 +4860,59 @@
         <v>52</v>
       </c>
       <c r="O27" s="5">
-        <v>7545.2600000000002</v>
+        <v>40656.57</v>
       </c>
       <c r="P27" s="5">
-        <v>26408.41</v>
+        <v>40656.57</v>
       </c>
       <c r="Q27" s="6">
-        <v>-0.25983655444803078</v>
+        <v>0.13950468564842877</v>
       </c>
       <c r="R27" s="7">
-        <v>241.5</v>
+        <v>399</v>
       </c>
       <c r="S27" s="6">
-        <v>-0.11538461538461542</v>
+        <v>0.007575757575757569</v>
       </c>
       <c r="T27" s="6">
-        <v>0.25522705645663635</v>
+        <v>0.3036675868131522</v>
       </c>
       <c r="U27" s="6">
-        <v>-0.061807744199669723</v>
+        <v>0.02298798201619074</v>
       </c>
       <c r="V27" s="6">
-        <v>0.046671552736419951</v>
+        <v>0.04552179389456612</v>
       </c>
       <c r="W27" s="6">
-        <v>0.0013702642453672902</v>
+        <v>0.0091749008831782906</v>
       </c>
       <c r="X27" s="8">
-        <v>24.59640588235294</v>
+        <v>29.148653535353539</v>
       </c>
       <c r="Y27" s="6">
-        <v>0.80392156862745101</v>
+        <v>0.70033670033670037</v>
       </c>
       <c r="Z27" s="6">
-        <v>0</v>
+        <v>0.10774410774410774</v>
       </c>
       <c r="AA27" s="8">
-        <v>5.6973044117647058</v>
+        <v>6.8558850515463918</v>
       </c>
       <c r="AB27" s="8">
-        <v>4.760416666666667</v>
+        <v>7.7732876712328771</v>
       </c>
       <c r="AC27" s="8">
-        <v>10.913683000000001</v>
+        <v>14.911220999999999</v>
       </c>
       <c r="AD27" s="8">
-        <v>17.348692156862747</v>
+        <v>21.663130976430974</v>
       </c>
       <c r="AE27" s="6">
-        <v>0.74509803921568629</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="AF27" s="9"/>
       <c r="AG27" s="5">
-        <v>0</v>
+        <v>-52.799999999999997</v>
       </c>
       <c r="AH27" s="10">
         <v>3</v>
@@ -5353,7 +5347,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5388,59 +5382,59 @@
         <v>52</v>
       </c>
       <c r="O31" s="5">
-        <v>31701.34</v>
+        <v>44442.239999999998</v>
       </c>
       <c r="P31" s="5">
-        <v>36984.896666666667</v>
+        <v>44442.239999999998</v>
       </c>
       <c r="Q31" s="6">
-        <v>-0.16816540506045929</v>
+        <v>-0.0004408274601321871</v>
       </c>
       <c r="R31" s="7">
-        <v>418.83333333333337</v>
+        <v>490</v>
       </c>
       <c r="S31" s="6">
-        <v>-0.14928909952606628</v>
+        <v>-0.11070780399274049</v>
       </c>
       <c r="T31" s="6">
-        <v>0.39801076232108801</v>
+        <v>0.37879158431258192</v>
       </c>
       <c r="U31" s="6">
-        <v>0.044461669443626041</v>
+        <v>0.029934506001497677</v>
       </c>
       <c r="V31" s="6">
-        <v>0.081945416187454545</v>
+        <v>0.069715466637145201</v>
       </c>
       <c r="W31" s="6">
-        <v>-0.010343111679190848</v>
+        <v>-0.013193270636223556</v>
       </c>
       <c r="X31" s="8">
-        <v>26.492029347826087</v>
+        <v>28.345644318181819</v>
       </c>
       <c r="Y31" s="6">
-        <v>0.77297297297297296</v>
+        <v>0.7094339622641509</v>
       </c>
       <c r="Z31" s="6">
-        <v>0.021739130434782608</v>
+        <v>0.079545454545454544</v>
       </c>
       <c r="AA31" s="8">
-        <v>3.352721282798834</v>
+        <v>3.6702181434599153</v>
       </c>
       <c r="AB31" s="8">
-        <v>7.5968304347826088</v>
+        <v>8.5334602272727285</v>
       </c>
       <c r="AC31" s="8">
-        <v>11.318809999999999</v>
+        <v>12.788659000000001</v>
       </c>
       <c r="AD31" s="8">
-        <v>18.192342702702703</v>
+        <v>19.663081886792451</v>
       </c>
       <c r="AE31" s="6">
-        <v>0.73913043478260865</v>
+        <v>0.62878787878787878</v>
       </c>
       <c r="AF31" s="9"/>
       <c r="AG31" s="5">
-        <v>2151.3000000000002</v>
+        <v>3546</v>
       </c>
       <c r="AH31" s="10">
         <v>3</v>
@@ -5871,7 +5865,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5908,55 +5902,55 @@
         <v>52</v>
       </c>
       <c r="O35" s="5">
-        <v>33208.779999999999</v>
+        <v>44939.209999999999</v>
       </c>
       <c r="P35" s="5">
-        <v>38743.576666666668</v>
+        <v>44939.209999999999</v>
       </c>
       <c r="Q35" s="6">
-        <v>-0.12193850405036666</v>
+        <v>0.018475663692245403</v>
       </c>
       <c r="R35" s="7">
-        <v>443.33333333333337</v>
+        <v>523</v>
       </c>
       <c r="S35" s="6">
-        <v>-0.23694779116465858</v>
+        <v>-0.19414483821263484</v>
       </c>
       <c r="T35" s="6">
-        <v>0.21757987797203029</v>
+        <v>0.21506830449400424</v>
       </c>
       <c r="U35" s="6">
-        <v>-0.10567770631742571</v>
+        <v>-0.10409551703289845</v>
       </c>
       <c r="V35" s="6">
-        <v>0.065505297093118156</v>
+        <v>0.053847141505157743</v>
       </c>
       <c r="W35" s="6">
-        <v>0.02497113715107872</v>
+        <v>0.018710564782959023</v>
       </c>
       <c r="X35" s="8">
-        <v>24.307163157894735</v>
+        <v>24.401253605015672</v>
       </c>
       <c r="Y35" s="6">
-        <v>0.93886462882096067</v>
+        <v>0.9375</v>
       </c>
       <c r="Z35" s="6">
-        <v>0.043859649122807015</v>
+        <v>0.037617554858934171</v>
       </c>
       <c r="AA35" s="8">
-        <v>3.626190740740741</v>
+        <v>3.6430637764932561</v>
       </c>
       <c r="AB35" s="8">
-        <v>5.3146606481481475</v>
+        <v>5.5147540983606556</v>
       </c>
       <c r="AC35" s="8">
-        <v>9.1310380000000002</v>
+        <v>9.3040210000000005</v>
       </c>
       <c r="AD35" s="8">
-        <v>16.55756899563319</v>
+        <v>16.822812500000001</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.80263157894736847</v>
+        <v>0.80877742946708464</v>
       </c>
       <c r="AF35" s="9"/>
       <c r="AG35" s="5">
@@ -6133,7 +6127,7 @@
         <v>19606</v>
       </c>
       <c r="B37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C37" s="4">
         <v>44</v>
@@ -6170,59 +6164,59 @@
         <v>52</v>
       </c>
       <c r="O37" s="5">
-        <v>33520.080000000002</v>
+        <v>43863.120000000003</v>
       </c>
       <c r="P37" s="5">
-        <v>39106.760000000002</v>
+        <v>43863.120000000003</v>
       </c>
       <c r="Q37" s="6">
-        <v>-0.03584270039664128</v>
+        <v>0.081422938933782163</v>
       </c>
       <c r="R37" s="7">
-        <v>385</v>
+        <v>451</v>
       </c>
       <c r="S37" s="6">
-        <v>-0.098360655737704916</v>
+        <v>-0.10869565217391319</v>
       </c>
       <c r="T37" s="6">
-        <v>-0.021007109768234441</v>
+        <v>0</v>
       </c>
       <c r="U37" s="6">
-        <v>-0.35031718301388298</v>
+        <v>-0.32572990703807664</v>
       </c>
       <c r="V37" s="6">
-        <v>0.041503093071376916</v>
+        <v>0.037764516067256497</v>
       </c>
       <c r="W37" s="6">
-        <v>0.021157974563306529</v>
+        <v>0.019305956803802371</v>
       </c>
       <c r="X37" s="8">
-        <v>22.852323636363636</v>
+        <v>23.500304566210048</v>
       </c>
       <c r="Y37" s="6">
         <v>1</v>
       </c>
       <c r="Z37" s="6">
-        <v>0.012121212121212121</v>
+        <v>0.0091324200913242004</v>
       </c>
       <c r="AA37" s="8">
-        <v>4.1761548192771087</v>
+        <v>4.1852057268722467</v>
       </c>
       <c r="AB37" s="8">
-        <v>2.5985611510791364</v>
+        <v>2.8498265625000001</v>
       </c>
       <c r="AC37" s="8">
-        <v>7.0408840000000001</v>
+        <v>7.2309580000000002</v>
       </c>
       <c r="AD37" s="8">
-        <v>14.138989696969698</v>
+        <v>14.489269406392694</v>
       </c>
       <c r="AE37" s="6">
-        <v>0.94545454545454544</v>
+        <v>0.9360730593607306</v>
       </c>
       <c r="AF37" s="9"/>
       <c r="AG37" s="5">
-        <v>-9870.4300000000003</v>
+        <v>-13047.030000000001</v>
       </c>
       <c r="AH37" s="10">
         <v>1</v>
@@ -6341,7 +6335,7 @@
         <v>3.45273237704918</v>
       </c>
       <c r="AC38" s="8">
-        <v>6.2119770000000001</v>
+        <v>6.9202110000000001</v>
       </c>
       <c r="AD38" s="8">
         <v>13.850683196721311</v>
@@ -6994,7 +6988,7 @@
         <v>2.4714285714285711</v>
       </c>
       <c r="AC43" s="8">
-        <v>11.192640000000001</v>
+        <v>11.312777000000001</v>
       </c>
       <c r="AD43" s="8">
         <v>12.99765625</v>
@@ -7138,7 +7132,7 @@
         <v>-1539.2</v>
       </c>
       <c r="AH44" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" s="11"/>
       <c r="AJ44" s="12">
@@ -7308,7 +7302,7 @@
         <v>19624</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -7343,59 +7337,59 @@
         <v>52</v>
       </c>
       <c r="O46" s="5">
-        <v>20419.949999999997</v>
+        <v>28968.609999999997</v>
       </c>
       <c r="P46" s="5">
-        <v>23823.274999999994</v>
+        <v>28968.609999999997</v>
       </c>
       <c r="Q46" s="6">
-        <v>-0.15021428991829711</v>
+        <v>0.033321859355186056</v>
       </c>
       <c r="R46" s="7">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="S46" s="6">
-        <v>-0.12455516014234891</v>
+        <v>-0.12436548223350252</v>
       </c>
       <c r="T46" s="6">
-        <v>0.44754056694556055</v>
+        <v>0.31107157367923421</v>
       </c>
       <c r="U46" s="6">
-        <v>0.11754514580104261</v>
+        <v>-0.017155773093703839</v>
       </c>
       <c r="V46" s="6">
-        <v>0.033110267165198742</v>
+        <v>0.030196754348931484</v>
       </c>
       <c r="W46" s="6">
-        <v>-0.023124444477092256</v>
+        <v>-0.016078852247311832</v>
       </c>
       <c r="X46" s="8">
-        <v>23.966235344827584</v>
+        <v>22.806444000000003</v>
       </c>
       <c r="Y46" s="6">
-        <v>0.93103448275862066</v>
+        <v>0.94666666666666666</v>
       </c>
       <c r="Z46" s="6">
-        <v>0.025862068965517241</v>
+        <v>0.02</v>
       </c>
       <c r="AA46" s="8">
-        <v>2.6403288065843622</v>
+        <v>2.5469295321637428</v>
       </c>
       <c r="AB46" s="8">
-        <v>5.0793945454545453</v>
+        <v>4.7299277372262774</v>
       </c>
       <c r="AC46" s="8">
-        <v>7.833666</v>
+        <v>7.4681160000000002</v>
       </c>
       <c r="AD46" s="8">
-        <v>14.310488793103447</v>
+        <v>13.648</v>
       </c>
       <c r="AE46" s="6">
-        <v>0.89655172413793105</v>
+        <v>0.91333333333333333</v>
       </c>
       <c r="AF46" s="9"/>
       <c r="AG46" s="5">
-        <v>0</v>
+        <v>-249</v>
       </c>
       <c r="AH46" s="10">
         <v>3</v>
@@ -8181,7 +8175,7 @@
         <v>19647</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>44</v>
@@ -8216,55 +8210,55 @@
         <v>52</v>
       </c>
       <c r="O53" s="5">
-        <v>30902.779999999999</v>
+        <v>38925.489999999998</v>
       </c>
       <c r="P53" s="5">
-        <v>36053.243333333332</v>
+        <v>38925.489999999998</v>
       </c>
       <c r="Q53" s="6">
-        <v>1.9677212859352822</v>
+        <v>2.2041501556575893</v>
       </c>
       <c r="R53" s="7">
-        <v>376.83333333333337</v>
+        <v>412</v>
       </c>
       <c r="S53" s="6">
-        <v>0.98159509202453998</v>
+        <v>1.5276073619631902</v>
       </c>
       <c r="T53" s="6">
-        <v>0.45525099683588338</v>
+        <v>0.36661987556226011</v>
       </c>
       <c r="U53" s="6">
-        <v>0.13281333912353518</v>
+        <v>0.04669223945543139</v>
       </c>
       <c r="V53" s="6">
-        <v>0.0215099580037783</v>
+        <v>0.021679418807573136</v>
       </c>
       <c r="W53" s="6">
-        <v>-0.015612592135723713</v>
+        <v>-0.01301943790559862</v>
       </c>
       <c r="X53" s="8">
-        <v>29.449704867256639</v>
+        <v>29.624712413793105</v>
       </c>
       <c r="Y53" s="6">
-        <v>0.77876106194690264</v>
+        <v>0.72413793103448276</v>
       </c>
       <c r="Z53" s="6">
-        <v>0.11061946902654868</v>
+        <v>0.11379310344827587</v>
       </c>
       <c r="AA53" s="8">
-        <v>4.5236196319018402</v>
+        <v>4.2098156250000001</v>
       </c>
       <c r="AB53" s="8">
-        <v>7.7235120535714286</v>
+        <v>8.1031578947368423</v>
       </c>
       <c r="AC53" s="8">
         <v>18.779319999999998</v>
       </c>
       <c r="AD53" s="8">
-        <v>19.817551769911503</v>
+        <v>19.784597931034483</v>
       </c>
       <c r="AE53" s="6">
-        <v>0.65044247787610621</v>
+        <v>0.61379310344827587</v>
       </c>
       <c r="AF53" s="9"/>
       <c r="AG53" s="5">
@@ -8441,7 +8435,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8476,59 +8470,59 @@
         <v>52</v>
       </c>
       <c r="O55" s="5">
-        <v>41888.790000000001</v>
+        <v>57506.889999999999</v>
       </c>
       <c r="P55" s="5">
-        <v>48870.255000000005</v>
+        <v>57506.889999999999</v>
       </c>
       <c r="Q55" s="6">
-        <v>0.0022186301771027761</v>
+        <v>0.17933652119362442</v>
       </c>
       <c r="R55" s="7">
-        <v>553</v>
+        <v>655</v>
       </c>
       <c r="S55" s="6">
-        <v>-0.10227272727272729</v>
+        <v>-0.091539528432732276</v>
       </c>
       <c r="T55" s="6">
-        <v>0.26247547136119231</v>
+        <v>0.27342369062211502</v>
       </c>
       <c r="U55" s="6">
-        <v>-0.061526248430666057</v>
+        <v>-0.049736716765591042</v>
       </c>
       <c r="V55" s="6">
-        <v>0.045946946665205657</v>
+        <v>0.041641618943399648</v>
       </c>
       <c r="W55" s="6">
-        <v>0.0073082082342316402</v>
+        <v>0.0073067766314610302</v>
       </c>
       <c r="X55" s="8">
-        <v>23.566319791666668</v>
+        <v>24.44939855595668</v>
       </c>
       <c r="Y55" s="6">
-        <v>0.90625</v>
+        <v>0.92779783393501802</v>
       </c>
       <c r="Z55" s="6">
-        <v>0.03125</v>
+        <v>0.036101083032490974</v>
       </c>
       <c r="AA55" s="8">
-        <v>2.1612326039387311</v>
+        <v>2.5226077287066246</v>
       </c>
       <c r="AB55" s="8">
-        <v>5.9620075268817194</v>
+        <v>6.4144279850746271</v>
       </c>
       <c r="AC55" s="8">
-        <v>8.2486899999999999</v>
+        <v>8.9660930000000008</v>
       </c>
       <c r="AD55" s="8">
-        <v>15.814843229166668</v>
+        <v>16.515884115523466</v>
       </c>
       <c r="AE55" s="6">
-        <v>0.890625</v>
+        <v>0.83754512635379064</v>
       </c>
       <c r="AF55" s="9"/>
       <c r="AG55" s="5">
-        <v>-991.60000000000002</v>
+        <v>-1218.7</v>
       </c>
       <c r="AH55" s="10">
         <v>5</v>
@@ -8919,7 +8913,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>44</v>
@@ -8956,59 +8950,59 @@
         <v>52</v>
       </c>
       <c r="O59" s="5">
-        <v>27408.859999999997</v>
+        <v>33942.679999999993</v>
       </c>
       <c r="P59" s="5">
-        <v>31977.00333333333</v>
+        <v>33942.679999999993</v>
       </c>
       <c r="Q59" s="6">
-        <v>0.1565287912719584</v>
+        <v>0.22762243427638906</v>
       </c>
       <c r="R59" s="7">
-        <v>345.33333333333337</v>
+        <v>365</v>
       </c>
       <c r="S59" s="6">
-        <v>0.21311475409836089</v>
+        <v>0.099397590361445687</v>
       </c>
       <c r="T59" s="6">
         <v>0</v>
       </c>
       <c r="U59" s="6">
-        <v>-0.32532400107118647</v>
+        <v>-0.31955873843786053</v>
       </c>
       <c r="V59" s="6">
-        <v>0.056034745699018493</v>
+        <v>0.054269462517396977</v>
       </c>
       <c r="W59" s="6">
-        <v>0.030011043874134127</v>
+        <v>0.029642355877614848</v>
       </c>
       <c r="X59" s="8">
-        <v>25.063457142857143</v>
+        <v>25.441336138613863</v>
       </c>
       <c r="Y59" s="6">
-        <v>0.7639751552795031</v>
+        <v>0.73762376237623761</v>
       </c>
       <c r="Z59" s="6">
-        <v>0.043478260869565216</v>
+        <v>0.059405940594059403</v>
       </c>
       <c r="AA59" s="8">
-        <v>6.4265283737024221</v>
+        <v>6.4841715083798883</v>
       </c>
       <c r="AB59" s="8">
-        <v>5.6128124999999995</v>
+        <v>6.0864014925373136</v>
       </c>
       <c r="AC59" s="8">
-        <v>12.225543999999999</v>
+        <v>12.817589</v>
       </c>
       <c r="AD59" s="8">
-        <v>18.971842857142857</v>
+        <v>19.597195049504951</v>
       </c>
       <c r="AE59" s="6">
-        <v>0.80745341614906829</v>
+        <v>0.79207920792079212</v>
       </c>
       <c r="AF59" s="9"/>
       <c r="AG59" s="5">
-        <v>-1313.3</v>
+        <v>-1496.9000000000001</v>
       </c>
       <c r="AH59" s="10">
         <v>3</v>
@@ -9179,7 +9173,7 @@
         <v>19666</v>
       </c>
       <c r="B61" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="s" r="C61" s="4">
         <v>44</v>
@@ -9214,55 +9208,55 @@
         <v>52</v>
       </c>
       <c r="O61" s="5">
-        <v>31410.589999999997</v>
+        <v>54441.879999999997</v>
       </c>
       <c r="P61" s="5">
-        <v>43974.825999999994</v>
+        <v>54441.879999999997</v>
       </c>
       <c r="Q61" s="6">
-        <v>-0.020075746940329098</v>
+        <v>0.21316952099285724</v>
       </c>
       <c r="R61" s="7">
-        <v>415.80000000000001</v>
+        <v>512</v>
       </c>
       <c r="S61" s="6">
-        <v>-0.099999999999999978</v>
+        <v>-0.080789946140035873</v>
       </c>
       <c r="T61" s="6">
-        <v>0.38152232734246633</v>
+        <v>0.2175079442517415</v>
       </c>
       <c r="U61" s="6">
-        <v>0.063758159270488071</v>
+        <v>-0.093553503295624632</v>
       </c>
       <c r="V61" s="6">
-        <v>0.044587080344558952</v>
+        <v>0.035349045624434722</v>
       </c>
       <c r="W61" s="6">
-        <v>0.020443312271434567</v>
+        <v>0.015533969436764491</v>
       </c>
       <c r="X61" s="8">
-        <v>29.869024528301885</v>
+        <v>28.684710192837468</v>
       </c>
       <c r="Y61" s="6">
-        <v>1</v>
+        <v>0.99449035812672182</v>
       </c>
       <c r="Z61" s="6">
-        <v>0.15566037735849056</v>
+        <v>0.099173553719008267</v>
       </c>
       <c r="AA61" s="8">
-        <v>5.4650272131147544</v>
+        <v>4.8083172744721692</v>
       </c>
       <c r="AB61" s="8">
-        <v>7.7515866666666664</v>
+        <v>7.4813013850415517</v>
       </c>
       <c r="AC61" s="8">
-        <v>13.003679999999999</v>
+        <v>12.203932999999999</v>
       </c>
       <c r="AD61" s="8">
-        <v>20.866588207547171</v>
+        <v>20.108402203856752</v>
       </c>
       <c r="AE61" s="6">
-        <v>0.61792452830188682</v>
+        <v>0.66115702479338845</v>
       </c>
       <c r="AF61" s="9"/>
       <c r="AG61" s="5">
@@ -9516,7 +9510,7 @@
         <v>3.5503442477876108</v>
       </c>
       <c r="AC63" s="8">
-        <v>8.4273910000000001</v>
+        <v>8.8887219999999996</v>
       </c>
       <c r="AD63" s="8">
         <v>18.344054054054055</v>
@@ -10578,7 +10572,7 @@
         <v>19693</v>
       </c>
       <c r="B72" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C72" s="4">
         <v>44</v>
@@ -10613,59 +10607,59 @@
         <v>52</v>
       </c>
       <c r="O72" s="5">
-        <v>15663.43</v>
+        <v>51413.779999999999</v>
       </c>
       <c r="P72" s="5">
-        <v>36548.003333333334</v>
+        <v>51413.779999999992</v>
       </c>
       <c r="Q72" s="6">
-        <v>-0.32077601661349353</v>
+        <v>-0.044503960064280035</v>
       </c>
       <c r="R72" s="7">
-        <v>352.33333333333337</v>
+        <v>498</v>
       </c>
       <c r="S72" s="6">
-        <v>-0.079268292682926678</v>
+        <v>-0.2006420545746388</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="6">
-        <v>-0.35193887928761453</v>
+        <v>-0.33211777076106835</v>
       </c>
       <c r="V72" s="6">
-        <v>0.025945562370438657</v>
+        <v>0.041479249337434437</v>
       </c>
       <c r="W72" s="6">
-        <v>0.0057207457115076325</v>
+        <v>0.023503134762703697</v>
       </c>
       <c r="X72" s="8">
-        <v>34.452564615384617</v>
+        <v>36.98671762452107</v>
       </c>
       <c r="Y72" s="6">
-        <v>0.75384615384615383</v>
+        <v>0.63984674329501912</v>
       </c>
       <c r="Z72" s="6">
-        <v>0.23076923076923078</v>
+        <v>0.32183908045977011</v>
       </c>
       <c r="AA72" s="8">
-        <v>5.4060402684563762</v>
+        <v>6.2329341317365268</v>
       </c>
       <c r="AB72" s="8">
-        <v>10.9052078125</v>
+        <v>12.5624</v>
       </c>
       <c r="AC72" s="8">
         <v>16.393888</v>
       </c>
       <c r="AD72" s="8">
-        <v>24.579744615384612</v>
+        <v>26.424457471264368</v>
       </c>
       <c r="AE72" s="6">
-        <v>0.41538461538461541</v>
+        <v>0.3946360153256705</v>
       </c>
       <c r="AF72" s="9"/>
       <c r="AG72" s="5">
-        <v>0</v>
+        <v>66.799999999999997</v>
       </c>
       <c r="AH72" s="10">
         <v>2</v>
@@ -13463,7 +13457,7 @@
         <v>19740</v>
       </c>
       <c r="B95" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C95" s="4">
         <v>44</v>
@@ -13500,59 +13494,59 @@
         <v>52</v>
       </c>
       <c r="O95" s="5">
-        <v>34368.549999999996</v>
+        <v>51529.839999999997</v>
       </c>
       <c r="P95" s="5">
-        <v>40096.641666666663</v>
+        <v>51529.840000000004</v>
       </c>
       <c r="Q95" s="6">
-        <v>-0.048056027742429896</v>
+        <v>0.22338227194165317</v>
       </c>
       <c r="R95" s="7">
-        <v>374.5</v>
+        <v>475</v>
       </c>
       <c r="S95" s="6">
-        <v>-0.095774647887323816</v>
+        <v>-0.06311637080867849</v>
       </c>
       <c r="T95" s="6">
-        <v>0.30783621945063144</v>
+        <v>0.30155530077329956</v>
       </c>
       <c r="U95" s="6">
-        <v>0.022154687934172374</v>
+        <v>0.017323678862577491</v>
       </c>
       <c r="V95" s="6">
-        <v>0.028389603285561945</v>
+        <v>0.022938747723649056</v>
       </c>
       <c r="W95" s="6">
-        <v>0.017904726850565416</v>
+        <v>0.013779976805672211</v>
       </c>
       <c r="X95" s="8">
-        <v>25.427552252252251</v>
+        <v>28.984070501474925</v>
       </c>
       <c r="Y95" s="6">
-        <v>0.85585585585585588</v>
+        <v>0.69911504424778759</v>
       </c>
       <c r="Z95" s="6">
-        <v>0.067567567567567571</v>
+        <v>0.15929203539823009</v>
       </c>
       <c r="AA95" s="8">
-        <v>4.6985140127388538</v>
+        <v>7.2749469083155649</v>
       </c>
       <c r="AB95" s="8">
-        <v>3.6339800970873788</v>
+        <v>4.4577081249999999</v>
       </c>
       <c r="AC95" s="8">
-        <v>8.5839390000000009</v>
+        <v>12.118306</v>
       </c>
       <c r="AD95" s="8">
-        <v>16.051651351351353</v>
+        <v>19.613913274336284</v>
       </c>
       <c r="AE95" s="6">
-        <v>0.73873873873873874</v>
+        <v>0.60766961651917406</v>
       </c>
       <c r="AF95" s="9"/>
       <c r="AG95" s="5">
-        <v>-986.60000000000002</v>
+        <v>-1221.8</v>
       </c>
       <c r="AH95" s="10">
         <v>4</v>
@@ -13725,7 +13719,7 @@
         <v>19742</v>
       </c>
       <c r="B97" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>44</v>
@@ -13759,25 +13753,61 @@
       <c t="s" r="N97" s="4">
         <v>52</v>
       </c>
-      <c r="O97" s="5"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="7"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
-      <c r="X97" s="8"/>
-      <c r="Y97" s="6"/>
-      <c r="Z97" s="6"/>
-      <c r="AA97" s="8"/>
-      <c r="AB97" s="8"/>
-      <c r="AC97" s="8"/>
-      <c r="AD97" s="8"/>
-      <c r="AE97" s="6"/>
+      <c r="O97" s="5">
+        <v>30445.050000000003</v>
+      </c>
+      <c r="P97" s="5">
+        <v>30445.050000000007</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>-0.11777745773698767</v>
+      </c>
+      <c r="R97" s="7">
+        <v>294</v>
+      </c>
+      <c r="S97" s="6">
+        <v>-0.18105849582172706</v>
+      </c>
+      <c r="T97" s="6">
+        <v>0.21057905308087849</v>
+      </c>
+      <c r="U97" s="6">
+        <v>-0.079387953049838977</v>
+      </c>
+      <c r="V97" s="6">
+        <v>0.014297447368291397</v>
+      </c>
+      <c r="W97" s="6">
+        <v>-0.0076811665607381171</v>
+      </c>
+      <c r="X97" s="8">
+        <v>31.858108108108109</v>
+      </c>
+      <c r="Y97" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z97" s="6">
+        <v>0.21621621621621623</v>
+      </c>
+      <c r="AA97" s="8">
+        <v>7.0313217241379311</v>
+      </c>
+      <c r="AB97" s="8">
+        <v>11.386744444444444</v>
+      </c>
+      <c r="AC97" s="8">
+        <v>18.032889999999998</v>
+      </c>
+      <c r="AD97" s="8">
+        <v>24.8928827027027</v>
+      </c>
+      <c r="AE97" s="6">
+        <v>0.53513513513513511</v>
+      </c>
       <c r="AF97" s="9"/>
-      <c r="AG97" s="5"/>
+      <c r="AG97" s="5">
+        <v>-825.60000000000002</v>
+      </c>
       <c r="AH97" s="10">
         <v>2</v>
       </c>
@@ -15517,7 +15547,7 @@
         <v>19772</v>
       </c>
       <c r="B111" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C111" s="4">
         <v>44</v>
@@ -15554,60 +15584,60 @@
         <v>52</v>
       </c>
       <c r="O111" s="5">
-        <v>23323.130000000001</v>
+        <v>28780.279999999999</v>
       </c>
       <c r="P111" s="5">
-        <v>27210.318333333333</v>
+        <v>28780.279999999999</v>
       </c>
       <c r="Q111" s="6">
-        <v>0.18642677086985016</v>
+        <v>0.25488038202407881</v>
       </c>
       <c r="R111" s="7">
-        <v>262.5</v>
+        <v>279</v>
       </c>
       <c r="S111" s="6">
-        <v>-0.046610169491525522</v>
+        <v>-0.04123711340206182</v>
       </c>
       <c r="T111" s="6">
         <v>0</v>
       </c>
       <c r="U111" s="6">
-        <v>-0.28566748974087097</v>
+        <v>-0.28672827366516246</v>
       </c>
       <c r="V111" s="6">
-        <v>0.034716802590389881</v>
+        <v>0.03075465214375955</v>
       </c>
       <c r="W111" s="6">
-        <v>0.025397727491978994</v>
+        <v>0.021708180045503383</v>
       </c>
       <c r="X111" s="8">
-        <v>30.3398</v>
+        <v>30.685713095238096</v>
       </c>
       <c r="Y111" s="6">
-        <v>0.97014925373134331</v>
+        <v>0.97619047619047616</v>
       </c>
       <c r="Z111" s="6"/>
       <c r="AA111" s="8">
-        <v>7.6693023255813957</v>
+        <v>8.0776728301886784</v>
       </c>
       <c r="AB111" s="8">
-        <v>9.1895828124999994</v>
+        <v>10.008435802469137</v>
       </c>
       <c r="AC111" s="8">
-        <v>17.482475000000001</v>
+        <v>18.668631999999999</v>
       </c>
       <c r="AD111" s="8">
-        <v>23.774745454545453</v>
+        <v>25.086143373493975</v>
       </c>
       <c r="AE111" s="6">
-        <v>0.67164179104477617</v>
+        <v>0.59523809523809523</v>
       </c>
       <c r="AF111" s="9"/>
       <c r="AG111" s="5">
-        <v>-1770.9000000000001</v>
+        <v>-2618.1999999999998</v>
       </c>
       <c r="AH111" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="12">
@@ -16989,7 +17019,7 @@
         <v>9.7738854651162796</v>
       </c>
       <c r="AC122" s="8">
-        <v>15.272778000000001</v>
+        <v>18.837529</v>
       </c>
       <c r="AD122" s="8">
         <v>26.151160445682454</v>
@@ -17172,7 +17202,7 @@
         <v>19804</v>
       </c>
       <c r="B124" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C124" s="4">
         <v>44</v>
@@ -17209,59 +17239,59 @@
         <v>52</v>
       </c>
       <c r="O124" s="5">
-        <v>17714.540000000001</v>
+        <v>21920.360000000001</v>
       </c>
       <c r="P124" s="5">
-        <v>20666.963333333333</v>
+        <v>21920.360000000004</v>
       </c>
       <c r="Q124" s="6">
-        <v>0.071891787507764704</v>
+        <v>0.13689918950584601</v>
       </c>
       <c r="R124" s="7">
-        <v>247.33333333333334</v>
+        <v>261</v>
       </c>
       <c r="S124" s="6">
-        <v>0.08163265306122458</v>
+        <v>0.078512396694214948</v>
       </c>
       <c r="T124" s="6">
-        <v>0.32935420281870142</v>
+        <v>0.33833681563623952</v>
       </c>
       <c r="U124" s="6">
-        <v>0.020631537708571603</v>
+        <v>0.029980566012601982</v>
       </c>
       <c r="V124" s="6">
-        <v>0.055354217495910137</v>
+        <v>0.052512367497614086</v>
       </c>
       <c r="W124" s="6">
-        <v>0.0087817408750100207</v>
+        <v>0.0064939626903937706</v>
       </c>
       <c r="X124" s="8">
-        <v>23.482020606060605</v>
+        <v>26.706472815533981</v>
       </c>
       <c r="Y124" s="6">
-        <v>0.58787878787878789</v>
+        <v>0.57281553398058249</v>
       </c>
       <c r="Z124" s="6">
-        <v>0.078787878787878782</v>
+        <v>0.12135922330097088</v>
       </c>
       <c r="AA124" s="8">
-        <v>5.6294572093023252</v>
+        <v>7.1807835820895525</v>
       </c>
       <c r="AB124" s="8">
-        <v>6.9371428571428568</v>
+        <v>8.3126984126984134</v>
       </c>
       <c r="AC124" s="8">
-        <v>12.495872</v>
+        <v>15.659029</v>
       </c>
       <c r="AD124" s="8">
-        <v>15.655757575757574</v>
+        <v>18.030825242718446</v>
       </c>
       <c r="AE124" s="6">
-        <v>0.84242424242424241</v>
+        <v>0.72815533980582525</v>
       </c>
       <c r="AF124" s="9"/>
       <c r="AG124" s="5">
-        <v>-123.3</v>
+        <v>-223.19999999999999</v>
       </c>
       <c r="AH124" s="10">
         <v>1</v>
@@ -17698,7 +17728,7 @@
         <v>19817</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>44</v>
@@ -17735,53 +17765,53 @@
         <v>52</v>
       </c>
       <c r="O128" s="5">
-        <v>29428.880000000005</v>
+        <v>33659.770000000004</v>
       </c>
       <c r="P128" s="5">
-        <v>34333.693333333336</v>
+        <v>33659.770000000004</v>
       </c>
       <c r="Q128" s="6">
-        <v>0.38208861456730325</v>
+        <v>0.35496010971790004</v>
       </c>
       <c r="R128" s="7">
-        <v>373.33333333333337</v>
+        <v>370</v>
       </c>
       <c r="S128" s="6"/>
       <c r="T128" s="6">
-        <v>0.33932317165994763</v>
+        <v>0.33305687472017786</v>
       </c>
       <c r="U128" s="6">
-        <v>0.0069846660831129155</v>
+        <v>0.0025148062509042697</v>
       </c>
       <c r="V128" s="6">
-        <v>0.025091678650359779</v>
+        <v>0.026444120087570414</v>
       </c>
       <c r="W128" s="6">
-        <v>-0.027235151320743431</v>
+        <v>-0.027085360357483136</v>
       </c>
       <c r="X128" s="8">
-        <v>37.354637826086957</v>
+        <v>37.214968679245288</v>
       </c>
       <c r="Y128" s="6">
-        <v>0.37391304347826088</v>
+        <v>0.36603773584905658</v>
       </c>
       <c r="Z128" s="6">
-        <v>0.33913043478260868</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="AA128" s="8">
-        <v>8.7368034700315444</v>
+        <v>8.5215393442622958</v>
       </c>
       <c r="AB128" s="8">
-        <v>11.321165044247786</v>
+        <v>11.295192307692307</v>
       </c>
       <c r="AC128" s="8">
-        <v>20.949884000000001</v>
+        <v>20.706600999999999</v>
       </c>
       <c r="AD128" s="8">
-        <v>27.688333043478263</v>
+        <v>27.439622264150941</v>
       </c>
       <c r="AE128" s="6">
-        <v>0.32608695652173914</v>
+        <v>0.32830188679245281</v>
       </c>
       <c r="AF128" s="9"/>
       <c r="AG128" s="5">
@@ -17877,10 +17907,10 @@
         <v>-0.21148036253776437</v>
       </c>
       <c r="T129" s="6">
-        <v>0.29362284311457576</v>
+        <v>0.29457740774329572</v>
       </c>
       <c r="U129" s="6">
-        <v>0.0096215560071815469</v>
+        <v>0.010576120635901493</v>
       </c>
       <c r="V129" s="6">
         <v>0.031782547688209442</v>
@@ -17958,7 +17988,7 @@
         <v>19821</v>
       </c>
       <c r="B130" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="s" r="C130" s="4">
         <v>44</v>
@@ -17995,55 +18025,55 @@
         <v>52</v>
       </c>
       <c r="O130" s="5">
-        <v>14625.459999999999</v>
+        <v>29407.669999999998</v>
       </c>
       <c r="P130" s="5">
-        <v>20475.644</v>
+        <v>29407.670000000002</v>
       </c>
       <c r="Q130" s="6">
-        <v>-0.1108934382308574</v>
+        <v>0.27695873025246787</v>
       </c>
       <c r="R130" s="7">
-        <v>214.20000000000002</v>
+        <v>301</v>
       </c>
       <c r="S130" s="6">
-        <v>0.040816326530612512</v>
+        <v>0.13584905660377355</v>
       </c>
       <c r="T130" s="6">
-        <v>0.29256375525966366</v>
+        <v>0.27609326410422863</v>
       </c>
       <c r="U130" s="6">
-        <v>-0.0069953697182857846</v>
+        <v>-0.02714871324385781</v>
       </c>
       <c r="V130" s="6">
-        <v>0.05187929131801667</v>
+        <v>0.040474219820883471</v>
       </c>
       <c r="W130" s="6">
-        <v>0.0086936410888956654</v>
+        <v>0.0082870387215308108</v>
       </c>
       <c r="X130" s="8">
-        <v>22.059275</v>
+        <v>23.339960240963855</v>
       </c>
       <c r="Y130" s="6">
-        <v>0.87096774193548387</v>
+        <v>0.76000000000000001</v>
       </c>
       <c r="Z130" s="6">
-        <v>0</v>
+        <v>0.020080321285140562</v>
       </c>
       <c r="AA130" s="8">
-        <v>4.1510273972602736</v>
+        <v>4.6906845117845117</v>
       </c>
       <c r="AB130" s="8">
-        <v>1.8844254098360655</v>
+        <v>2.4360527196652719</v>
       </c>
       <c r="AC130" s="8">
-        <v>6.0367670000000002</v>
+        <v>7.167592</v>
       </c>
       <c r="AD130" s="8">
-        <v>12.769220967741935</v>
+        <v>13.720281526104419</v>
       </c>
       <c r="AE130" s="6">
-        <v>0.97580645161290325</v>
+        <v>0.90361445783132532</v>
       </c>
       <c r="AF130" s="9"/>
       <c r="AG130" s="5">
@@ -19192,7 +19222,7 @@
         <v>19868</v>
       </c>
       <c r="B140" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C140" s="4">
         <v>44</v>
@@ -19229,31 +19259,31 @@
         <v>52</v>
       </c>
       <c r="O140" s="5">
-        <v>19774.099999999999</v>
+        <v>27122.449999999997</v>
       </c>
       <c r="P140" s="5">
-        <v>23069.783333333329</v>
+        <v>27122.449999999993</v>
       </c>
       <c r="Q140" s="6">
-        <v>-0.0046320066525321613</v>
+        <v>0.17022419504736108</v>
       </c>
       <c r="R140" s="7">
-        <v>304.5</v>
+        <v>363</v>
       </c>
       <c r="S140" s="6">
-        <v>-0.11824324324324331</v>
+        <v>-0.052219321148825104</v>
       </c>
       <c r="T140" s="6">
-        <v>0.11651321678357043</v>
+        <v>0.076797413213039387</v>
       </c>
       <c r="U140" s="6">
-        <v>-0.20259966319579653</v>
+        <v>-0.23715025744355689</v>
       </c>
       <c r="V140" s="6">
-        <v>0.018584385635755866</v>
+        <v>0.015078560380791558</v>
       </c>
       <c r="W140" s="6">
-        <v>-0.029567489797260052</v>
+        <v>-0.025716795495982114</v>
       </c>
       <c r="X140" s="8">
         <v>6.9000000000000004</v>
@@ -19265,7 +19295,7 @@
         <v>0</v>
       </c>
       <c r="AA140" s="8">
-        <v>11.950000000000001</v>
+        <v>11.293984319526627</v>
       </c>
       <c r="AB140" s="8"/>
       <c r="AC140" s="8"/>
@@ -19277,7 +19307,7 @@
       </c>
       <c r="AF140" s="9"/>
       <c r="AG140" s="5">
-        <v>-3952.0999999999999</v>
+        <v>-5671.8500000000004</v>
       </c>
       <c r="AH140" s="10">
         <v>2</v>
@@ -19974,7 +20004,7 @@
         <v>19881</v>
       </c>
       <c r="B146" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="s" r="C146" s="4">
         <v>44</v>
@@ -20011,59 +20041,59 @@
         <v>52</v>
       </c>
       <c r="O146" s="5">
-        <v>45763.720000000001</v>
+        <v>74289.520000000004</v>
       </c>
       <c r="P146" s="5">
-        <v>64069.208000000006</v>
+        <v>74289.520000000004</v>
       </c>
       <c r="Q146" s="6">
-        <v>-0.091816180302019212</v>
+        <v>0.053057188363082819</v>
       </c>
       <c r="R146" s="7">
-        <v>575.39999999999998</v>
+        <v>661</v>
       </c>
       <c r="S146" s="6">
-        <v>-0.074324324324324342</v>
+        <v>-0.080667593880389465</v>
       </c>
       <c r="T146" s="6">
-        <v>4.2856078155359745</v>
+        <v>3.0126924201421681</v>
       </c>
       <c r="U146" s="6">
-        <v>3.9680479668173829</v>
+        <v>2.7010970564892594</v>
       </c>
       <c r="V146" s="6">
-        <v>0.031065700078577528</v>
+        <v>0.026543945902463763</v>
       </c>
       <c r="W146" s="6">
-        <v>0.0048630662017860437</v>
+        <v>0.0028913499508409798</v>
       </c>
       <c r="X146" s="8">
-        <v>23.482737857142855</v>
+        <v>24.979948908296944</v>
       </c>
       <c r="Y146" s="6">
-        <v>0.94999999999999996</v>
+        <v>0.86462882096069871</v>
       </c>
       <c r="Z146" s="6">
-        <v>0.021428571428571429</v>
+        <v>0.063318777292576414</v>
       </c>
       <c r="AA146" s="8">
-        <v>3.1154619277108435</v>
+        <v>3.3986317910447759</v>
       </c>
       <c r="AB146" s="8">
-        <v>7.3269090909090915</v>
+        <v>8.5142329646017707</v>
       </c>
       <c r="AC146" s="8">
-        <v>10.247192999999999</v>
+        <v>11.785874</v>
       </c>
       <c r="AD146" s="8">
-        <v>16.320892857142859</v>
+        <v>17.893741048034933</v>
       </c>
       <c r="AE146" s="6">
-        <v>0.84999999999999998</v>
+        <v>0.78602620087336239</v>
       </c>
       <c r="AF146" s="9"/>
       <c r="AG146" s="5">
-        <v>0</v>
+        <v>-28525.799999999999</v>
       </c>
       <c r="AH146" s="10">
         <v>5</v>
@@ -20760,7 +20790,7 @@
         <v>19891</v>
       </c>
       <c r="B152" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C152" s="4">
         <v>44</v>
@@ -20797,55 +20827,55 @@
         <v>52</v>
       </c>
       <c r="O152" s="5">
-        <v>26290.110000000004</v>
+        <v>32219.430000000004</v>
       </c>
       <c r="P152" s="5">
-        <v>30671.795000000002</v>
+        <v>32219.430000000004</v>
       </c>
       <c r="Q152" s="6">
-        <v>0.26636726217264051</v>
+        <v>0.33026552107116758</v>
       </c>
       <c r="R152" s="7">
-        <v>268.33333333333337</v>
+        <v>284</v>
       </c>
       <c r="S152" s="6">
-        <v>-0.045643153526970681</v>
+        <v>-0.046979865771812124</v>
       </c>
       <c r="T152" s="6">
-        <v>-0.18187646228943127</v>
+        <v>-0.11890364292602321</v>
       </c>
       <c r="U152" s="6">
-        <v>-0.48660588335309363</v>
+        <v>-0.41673727933734395</v>
       </c>
       <c r="V152" s="6">
-        <v>0.028971255730767198</v>
+        <v>0.025879585703409404</v>
       </c>
       <c r="W152" s="6">
-        <v>-0.016177661485630906</v>
+        <v>-0.015595387627900307</v>
       </c>
       <c r="X152" s="8">
-        <v>36.757475735294122</v>
+        <v>31.835082872928176</v>
       </c>
       <c r="Y152" s="6">
-        <v>0.63235294117647056</v>
+        <v>0.59116022099447518</v>
       </c>
       <c r="Z152" s="6">
-        <v>0.26470588235294118</v>
+        <v>0.19889502762430938</v>
       </c>
       <c r="AA152" s="8">
-        <v>9.2607985915492961</v>
+        <v>8.2542609022556395</v>
       </c>
       <c r="AB152" s="8">
-        <v>11.291730232558139</v>
+        <v>9.153713855421687</v>
       </c>
       <c r="AC152" s="8">
-        <v>20.415330999999998</v>
+        <v>17.093823</v>
       </c>
       <c r="AD152" s="8">
-        <v>26.523774264705882</v>
+        <v>22.968323756906077</v>
       </c>
       <c r="AE152" s="6">
-        <v>0.49264705882352944</v>
+        <v>0.61878453038674031</v>
       </c>
       <c r="AF152" s="9"/>
       <c r="AG152" s="5">
@@ -21361,7 +21391,7 @@
         <v>3.2694447154471544</v>
       </c>
       <c r="AC156" s="8">
-        <v>6.4655040000000001</v>
+        <v>6.3646529999999997</v>
       </c>
       <c r="AD156" s="8">
         <v>13.321070325203252</v>
@@ -21490,7 +21520,7 @@
         <v>1.8467644688644689</v>
       </c>
       <c r="AC157" s="8">
-        <v>6.0488150000000003</v>
+        <v>6.8875510000000002</v>
       </c>
       <c r="AD157" s="8">
         <v>13.822161538461538</v>
@@ -21537,16 +21567,16 @@
     </row>
     <row r="158" ht="13.5" customHeight="1">
       <c r="A158" s="2">
-        <v>19905</v>
+        <v>19908</v>
       </c>
       <c r="B158" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D158" s="4">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c t="s" r="E158" s="4">
         <v>240</v>
@@ -21576,31 +21606,67 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>19175.279999999999</v>
+      </c>
+      <c r="P158" s="5">
+        <v>19175.279999999999</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.26998424635682716</v>
+      </c>
+      <c r="R158" s="7">
+        <v>217</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.40220385674931125</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.29533048800330425</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.026294020217696952</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.023960067336695996</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.045605540049480378</v>
+      </c>
+      <c r="X158" s="8">
+        <v>24.506945238095238</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.5105500000000003</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>7.4310412499999998</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>13.233124</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>20.804563095238095</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.76190476190476186</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-366.60000000000002</v>
+      </c>
       <c r="AH158" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI158" s="11"/>
       <c r="AJ158" s="12">
-        <v>45965</v>
+        <v>44783</v>
       </c>
       <c t="s" r="AK158" s="4">
         <v>52</v>
@@ -21632,7 +21698,7 @@
     </row>
     <row r="159" ht="13.5" customHeight="1">
       <c r="A159" s="2">
-        <v>19908</v>
+        <v>19910</v>
       </c>
       <c r="B159" s="3">
         <v>0</v>
@@ -21641,7 +21707,7 @@
         <v>44</v>
       </c>
       <c t="s" r="D159" s="4">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c t="s" r="E159" s="4">
         <v>242</v>
@@ -21672,66 +21738,66 @@
         <v>52</v>
       </c>
       <c r="O159" s="5">
-        <v>19175.279999999999</v>
+        <v>30128.459999999999</v>
       </c>
       <c r="P159" s="5">
-        <v>19175.279999999999</v>
+        <v>30128.459999999999</v>
       </c>
       <c r="Q159" s="6">
-        <v>-0.26998424635682716</v>
+        <v>0.22864383085688922</v>
       </c>
       <c r="R159" s="7">
-        <v>217</v>
+        <v>331</v>
       </c>
       <c r="S159" s="6">
-        <v>-0.40220385674931125</v>
+        <v>0.14930555555555558</v>
       </c>
       <c r="T159" s="6">
-        <v>0.40612502659674332</v>
+        <v>-0.0014019966503432304</v>
       </c>
       <c r="U159" s="6">
-        <v>0.084500518375742101</v>
+        <v>-0.30676576233899772</v>
       </c>
       <c r="V159" s="6">
-        <v>0.023960067336695996</v>
+        <v>0.06585650245648135</v>
       </c>
       <c r="W159" s="6">
-        <v>-0.045605540049480378</v>
+        <v>0.038535822939506373</v>
       </c>
       <c r="X159" s="8">
-        <v>24.506945238095238</v>
+        <v>19.949812359550563</v>
       </c>
       <c r="Y159" s="6">
-        <v>0.6428571428571429</v>
+        <v>0.8202247191011236</v>
       </c>
       <c r="Z159" s="6">
-        <v>0.083333333333333329</v>
+        <v>0.016853932584269662</v>
       </c>
       <c r="AA159" s="8">
-        <v>5.5105500000000003</v>
+        <v>5.1124101538461542</v>
       </c>
       <c r="AB159" s="8">
-        <v>7.4310412499999998</v>
+        <v>3.0384714285714285</v>
       </c>
       <c r="AC159" s="8">
-        <v>13.233124</v>
+        <v>8.0638290000000001</v>
       </c>
       <c r="AD159" s="8">
-        <v>20.804563095238095</v>
+        <v>14.540074719101124</v>
       </c>
       <c r="AE159" s="6">
-        <v>0.76190476190476186</v>
+        <v>0.9269662921348315</v>
       </c>
       <c r="AF159" s="9"/>
       <c r="AG159" s="5">
-        <v>-366.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="AH159" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI159" s="11"/>
       <c r="AJ159" s="12">
-        <v>44783</v>
+        <v>46114</v>
       </c>
       <c t="s" r="AK159" s="4">
         <v>52</v>
@@ -21763,16 +21829,16 @@
     </row>
     <row r="160" ht="13.5" customHeight="1">
       <c r="A160" s="2">
-        <v>19910</v>
+        <v>19911</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D160" s="4">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c t="s" r="E160" s="4">
         <v>244</v>
@@ -21803,66 +21869,66 @@
         <v>52</v>
       </c>
       <c r="O160" s="5">
-        <v>22483.239999999998</v>
+        <v>33831.669999999998</v>
       </c>
       <c r="P160" s="5">
-        <v>26230.446666666667</v>
+        <v>33831.669999999998</v>
       </c>
       <c r="Q160" s="6">
-        <v>0.069682170201220028</v>
+        <v>0.1313698697935477</v>
       </c>
       <c r="R160" s="7">
-        <v>291.66666666666663</v>
+        <v>458</v>
       </c>
       <c r="S160" s="6">
-        <v>0.15740740740740722</v>
+        <v>-0.11923076923076925</v>
       </c>
       <c r="T160" s="6">
-        <v>0.0015922971955999222</v>
+        <v>0.1249528740378468</v>
       </c>
       <c r="U160" s="6">
-        <v>-0.30454062670682697</v>
+        <v>-0.18825336142141372</v>
       </c>
       <c r="V160" s="6">
-        <v>0.068410091250193469</v>
+        <v>0.073261030271340441</v>
       </c>
       <c r="W160" s="6">
-        <v>0.037305588518380797</v>
+        <v>0.053881850940258054</v>
       </c>
       <c r="X160" s="8">
-        <v>20.056342537313434</v>
+        <v>27.704783081570998</v>
       </c>
       <c r="Y160" s="6">
-        <v>0.86567164179104472</v>
+        <v>0.5226586102719033</v>
       </c>
       <c r="Z160" s="6">
-        <v>0.022388059701492536</v>
+        <v>0.12688821752265861</v>
       </c>
       <c r="AA160" s="8">
-        <v>4.9511563265306124</v>
+        <v>6.0824332613390926</v>
       </c>
       <c r="AB160" s="8">
-        <v>3.3234326732673267</v>
+        <v>7.7217574545454539</v>
       </c>
       <c r="AC160" s="8">
-        <v>8.1489539999999998</v>
+        <v>13.498384</v>
       </c>
       <c r="AD160" s="8">
-        <v>14.548880597014925</v>
+        <v>19.660674924471298</v>
       </c>
       <c r="AE160" s="6">
-        <v>0.91791044776119401</v>
+        <v>0.66465256797583083</v>
       </c>
       <c r="AF160" s="9"/>
       <c r="AG160" s="5">
-        <v>0</v>
+        <v>-1214.95</v>
       </c>
       <c r="AH160" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI160" s="11"/>
       <c r="AJ160" s="12">
-        <v>46114</v>
+        <v>46009</v>
       </c>
       <c t="s" r="AK160" s="4">
         <v>52</v>
@@ -21886,7 +21952,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR160" s="4">
-        <v>245</v>
+        <v>158</v>
       </c>
       <c t="s" r="AS160" s="4">
         <v>56</v>
@@ -21894,7 +21960,7 @@
     </row>
     <row r="161" ht="13.5" customHeight="1">
       <c r="A161" s="2">
-        <v>19911</v>
+        <v>19912</v>
       </c>
       <c r="B161" s="3">
         <v>0</v>
@@ -21903,10 +21969,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D161" s="4">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c t="s" r="E161" s="4">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="F161" s="4">
         <v>47</v>
@@ -21934,66 +22000,66 @@
         <v>52</v>
       </c>
       <c r="O161" s="5">
-        <v>33831.669999999998</v>
+        <v>33577.510000000002</v>
       </c>
       <c r="P161" s="5">
-        <v>33831.669999999998</v>
+        <v>33577.510000000002</v>
       </c>
       <c r="Q161" s="6">
-        <v>0.1313698697935477</v>
+        <v>1.0512590092869423</v>
       </c>
       <c r="R161" s="7">
-        <v>458</v>
+        <v>385</v>
       </c>
       <c r="S161" s="6">
-        <v>-0.11923076923076925</v>
+        <v>0.68122270742358082</v>
       </c>
       <c r="T161" s="6">
-        <v>0.1249528740378468</v>
+        <v>0.18384939800479547</v>
       </c>
       <c r="U161" s="6">
-        <v>-0.18825336142141372</v>
+        <v>-2.55908955130979</v>
       </c>
       <c r="V161" s="6">
-        <v>0.073261030271340441</v>
+        <v>0.014034125818144345</v>
       </c>
       <c r="W161" s="6">
-        <v>0.053881850940258054</v>
+        <v>-0.02691768984656694</v>
       </c>
       <c r="X161" s="8">
-        <v>27.704783081570998</v>
+        <v>22.034173949579831</v>
       </c>
       <c r="Y161" s="6">
-        <v>0.5226586102719033</v>
+        <v>0.81512605042016806</v>
       </c>
       <c r="Z161" s="6">
-        <v>0.12688821752265861</v>
+        <v>0</v>
       </c>
       <c r="AA161" s="8">
-        <v>6.0824332613390926</v>
+        <v>7.2181776000000006</v>
       </c>
       <c r="AB161" s="8">
-        <v>7.7217574545454539</v>
+        <v>1.3596176211453743</v>
       </c>
       <c r="AC161" s="8">
-        <v>13.498384</v>
+        <v>8.6107429999999994</v>
       </c>
       <c r="AD161" s="8">
-        <v>19.660674924471298</v>
+        <v>16.371498319327731</v>
       </c>
       <c r="AE161" s="6">
-        <v>0.66465256797583083</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="AF161" s="9"/>
       <c r="AG161" s="5">
-        <v>-1214.95</v>
+        <v>-459.74000000000001</v>
       </c>
       <c r="AH161" s="10">
         <v>4</v>
       </c>
       <c r="AI161" s="11"/>
       <c r="AJ161" s="12">
-        <v>46009</v>
+        <v>46003</v>
       </c>
       <c t="s" r="AK161" s="4">
         <v>52</v>
@@ -22017,7 +22083,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR161" s="4">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c t="s" r="AS161" s="4">
         <v>56</v>
@@ -22025,16 +22091,16 @@
     </row>
     <row r="162" ht="13.5" customHeight="1">
       <c r="A162" s="2">
-        <v>19912</v>
+        <v>19914</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D162" s="4">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c t="s" r="E162" s="4">
         <v>247</v>
@@ -22065,66 +22131,66 @@
         <v>52</v>
       </c>
       <c r="O162" s="5">
-        <v>26388.639999999999</v>
+        <v>47265.25</v>
       </c>
       <c r="P162" s="5">
-        <v>30786.746666666662</v>
+        <v>47265.25</v>
       </c>
       <c r="Q162" s="6">
-        <v>0.80715393170400329</v>
+        <v>0.42804032149394011</v>
       </c>
       <c r="R162" s="7">
-        <v>352.33333333333337</v>
+        <v>531</v>
       </c>
       <c r="S162" s="6">
-        <v>0.60638297872340452</v>
+        <v>0.1370449678800858</v>
       </c>
       <c r="T162" s="6">
-        <v>0.23385062663327857</v>
+        <v>0.26508317844505214</v>
       </c>
       <c r="U162" s="6">
-        <v>-2.6186048238939179</v>
+        <v>-0.0058293841670148793</v>
       </c>
       <c r="V162" s="6">
-        <v>0.015975396989007393</v>
+        <v>0.023328089875754385</v>
       </c>
       <c r="W162" s="6">
-        <v>-0.026912375931461417</v>
+        <v>0.010538990061408751</v>
       </c>
       <c r="X162" s="8">
-        <v>21.855846596858637</v>
+        <v>38.24029346590909</v>
       </c>
       <c r="Y162" s="6">
-        <v>0.82198952879581155</v>
+        <v>0.32386363636363635</v>
       </c>
       <c r="Z162" s="6">
-        <v>0</v>
+        <v>0.38920454545454547</v>
       </c>
       <c r="AA162" s="8">
-        <v>7.0407027210884356</v>
+        <v>6.7576678707224334</v>
       </c>
       <c r="AB162" s="8">
-        <v>1.4850725274725276</v>
+        <v>13.29295866261398</v>
       </c>
       <c r="AC162" s="8">
-        <v>8.4945459999999997</v>
+        <v>19.906573000000002</v>
       </c>
       <c r="AD162" s="8">
-        <v>16.245287434554974</v>
+        <v>27.735416761363638</v>
       </c>
       <c r="AE162" s="6">
-        <v>0.93193717277486909</v>
+        <v>0.375</v>
       </c>
       <c r="AF162" s="9"/>
       <c r="AG162" s="5">
-        <v>-364.04000000000002</v>
+        <v>-1169.3699999999999</v>
       </c>
       <c r="AH162" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI162" s="11"/>
       <c r="AJ162" s="12">
-        <v>46003</v>
+        <v>45996</v>
       </c>
       <c t="s" r="AK162" s="4">
         <v>52</v>
@@ -22156,19 +22222,19 @@
     </row>
     <row r="163" ht="13.5" customHeight="1">
       <c r="A163" s="2">
-        <v>19914</v>
+        <v>19923</v>
       </c>
       <c r="B163" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c t="s" r="C163" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D163" s="4">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c t="s" r="E163" s="4">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c t="s" r="F163" s="4">
         <v>47</v>
@@ -22195,68 +22261,30 @@
       <c t="s" r="N163" s="4">
         <v>52</v>
       </c>
-      <c r="O163" s="5">
-        <v>47265.25</v>
-      </c>
-      <c r="P163" s="5">
-        <v>47265.25</v>
-      </c>
-      <c r="Q163" s="6">
-        <v>0.26871999673594549</v>
-      </c>
-      <c r="R163" s="7">
-        <v>531</v>
-      </c>
-      <c r="S163" s="6">
-        <v>0.1370449678800858</v>
-      </c>
-      <c r="T163" s="6">
-        <v>0.26508317844505214</v>
-      </c>
-      <c r="U163" s="6">
-        <v>-0.0058293841670148793</v>
-      </c>
-      <c r="V163" s="6">
-        <v>0.023328089875754385</v>
-      </c>
-      <c r="W163" s="6">
-        <v>0.010538990061408751</v>
-      </c>
-      <c r="X163" s="8">
-        <v>38.24029346590909</v>
-      </c>
-      <c r="Y163" s="6">
-        <v>0.32386363636363635</v>
-      </c>
-      <c r="Z163" s="6">
-        <v>0.38920454545454547</v>
-      </c>
-      <c r="AA163" s="8">
-        <v>6.7576678707224334</v>
-      </c>
-      <c r="AB163" s="8">
-        <v>13.29295866261398</v>
-      </c>
-      <c r="AC163" s="8">
-        <v>19.906573000000002</v>
-      </c>
-      <c r="AD163" s="8">
-        <v>27.735416761363638</v>
-      </c>
-      <c r="AE163" s="6">
-        <v>0.375</v>
-      </c>
+      <c r="O163" s="5"/>
+      <c r="P163" s="5"/>
+      <c r="Q163" s="6"/>
+      <c r="R163" s="7"/>
+      <c r="S163" s="6"/>
+      <c r="T163" s="6"/>
+      <c r="U163" s="6"/>
+      <c r="V163" s="6"/>
+      <c r="W163" s="6"/>
+      <c r="X163" s="8"/>
+      <c r="Y163" s="6"/>
+      <c r="Z163" s="6"/>
+      <c r="AA163" s="8"/>
+      <c r="AB163" s="8"/>
+      <c r="AC163" s="8"/>
+      <c r="AD163" s="8"/>
+      <c r="AE163" s="6"/>
       <c r="AF163" s="9"/>
-      <c r="AG163" s="5">
-        <v>-1169.3699999999999</v>
-      </c>
+      <c r="AG163" s="5"/>
       <c r="AH163" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI163" s="11"/>
-      <c r="AJ163" s="12">
-        <v>45996</v>
-      </c>
+      <c r="AJ163" s="13"/>
       <c t="s" r="AK163" s="4">
         <v>52</v>
       </c>
@@ -22279,7 +22307,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR163" s="4">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c t="s" r="AS163" s="4">
         <v>56</v>
@@ -22287,19 +22315,19 @@
     </row>
     <row r="164" ht="13.5" customHeight="1">
       <c r="A164" s="2">
-        <v>19923</v>
+        <v>19926</v>
       </c>
       <c r="B164" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C164" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D164" s="4">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c t="s" r="E164" s="4">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c t="s" r="F164" s="4">
         <v>47</v>
@@ -22326,30 +22354,68 @@
       <c t="s" r="N164" s="4">
         <v>52</v>
       </c>
-      <c r="O164" s="5"/>
-      <c r="P164" s="5"/>
-      <c r="Q164" s="6"/>
-      <c r="R164" s="7"/>
-      <c r="S164" s="6"/>
-      <c r="T164" s="6"/>
-      <c r="U164" s="6"/>
-      <c r="V164" s="6"/>
-      <c r="W164" s="6"/>
-      <c r="X164" s="8"/>
-      <c r="Y164" s="6"/>
-      <c r="Z164" s="6"/>
-      <c r="AA164" s="8"/>
-      <c r="AB164" s="8"/>
-      <c r="AC164" s="8"/>
-      <c r="AD164" s="8"/>
-      <c r="AE164" s="6"/>
+      <c r="O164" s="5">
+        <v>14771.26</v>
+      </c>
+      <c r="P164" s="5">
+        <v>14771.26</v>
+      </c>
+      <c r="Q164" s="6">
+        <v>-0.052732092905138916</v>
+      </c>
+      <c r="R164" s="7">
+        <v>181</v>
+      </c>
+      <c r="S164" s="6">
+        <v>-0.28740157480314965</v>
+      </c>
+      <c r="T164" s="6">
+        <v>0.0078452345974547866</v>
+      </c>
+      <c r="U164" s="6">
+        <v>-0.30142289824970919</v>
+      </c>
+      <c r="V164" s="6">
+        <v>0.032821099892629338</v>
+      </c>
+      <c r="W164" s="6">
+        <v>-0.02464996215624124</v>
+      </c>
+      <c r="X164" s="8">
+        <v>33.642261904761902</v>
+      </c>
+      <c r="Y164" s="6">
+        <v>0.72619047619047616</v>
+      </c>
+      <c r="Z164" s="6">
+        <v>0.27380952380952384</v>
+      </c>
+      <c r="AA164" s="8">
+        <v>10.134225595238096</v>
+      </c>
+      <c r="AB164" s="8">
+        <v>11.499597590361445</v>
+      </c>
+      <c r="AC164" s="8">
+        <v>22.198605000000001</v>
+      </c>
+      <c r="AD164" s="8">
+        <v>28.747421428571425</v>
+      </c>
+      <c r="AE164" s="6">
+        <v>0.54761904761904767</v>
+      </c>
       <c r="AF164" s="9"/>
-      <c r="AG164" s="5"/>
+      <c r="AG164" s="5">
+        <v>-670.5</v>
+      </c>
       <c r="AH164" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI164" s="11"/>
-      <c r="AJ164" s="13"/>
+      <c r="AJ164" s="12">
+        <v>46014</v>
+      </c>
       <c t="s" r="AK164" s="4">
         <v>52</v>
       </c>
@@ -22380,7 +22446,7 @@
     </row>
     <row r="165" ht="13.5" customHeight="1">
       <c r="A165" s="2">
-        <v>19926</v>
+        <v>19927</v>
       </c>
       <c r="B165" s="3">
         <v>0</v>
@@ -22420,66 +22486,68 @@
         <v>52</v>
       </c>
       <c r="O165" s="5">
-        <v>14771.26</v>
+        <v>11989.599999999999</v>
       </c>
       <c r="P165" s="5">
-        <v>14771.26</v>
+        <v>11989.599999999997</v>
       </c>
       <c r="Q165" s="6">
-        <v>-0.13377846793318526</v>
+        <v>-0.059481356086433457</v>
       </c>
       <c r="R165" s="7">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="S165" s="6">
-        <v>-0.28740157480314965</v>
+        <v>-0.1166666666666667</v>
       </c>
       <c r="T165" s="6">
-        <v>0.0078452345974547866</v>
+        <v>0</v>
       </c>
       <c r="U165" s="6">
-        <v>-0.30142289824970919</v>
+        <v>-0.32360796023220123</v>
       </c>
       <c r="V165" s="6">
-        <v>0.032821099892629338</v>
+        <v>0.16152598919063188</v>
       </c>
       <c r="W165" s="6">
-        <v>-0.02464996215624124</v>
+        <v>0.084977980916794552</v>
       </c>
       <c r="X165" s="8">
-        <v>33.642261904761902</v>
+        <v>33.328411428571428</v>
       </c>
       <c r="Y165" s="6">
-        <v>0.72619047619047616</v>
+        <v>0.69811320754716977</v>
       </c>
       <c r="Z165" s="6">
-        <v>0.27380952380952384</v>
+        <v>0.22857142857142856</v>
       </c>
       <c r="AA165" s="8">
-        <v>10.134225595238096</v>
+        <v>7.0078622641509432</v>
       </c>
       <c r="AB165" s="8">
-        <v>11.499597590361445</v>
+        <v>10.546794230769232</v>
       </c>
       <c r="AC165" s="8">
-        <v>22.198605000000001</v>
+        <v>17.516887000000001</v>
       </c>
       <c r="AD165" s="8">
-        <v>28.747421428571425</v>
+        <v>24.352062857142858</v>
       </c>
       <c r="AE165" s="6">
-        <v>0.54761904761904767</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AF165" s="9"/>
       <c r="AG165" s="5">
-        <v>-670.5</v>
+        <v>-1033.5999999999999</v>
       </c>
       <c r="AH165" s="10">
-        <v>2</v>
-      </c>
-      <c r="AI165" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI165" s="11">
+        <v>4</v>
+      </c>
       <c r="AJ165" s="12">
-        <v>46014</v>
+        <v>45984</v>
       </c>
       <c t="s" r="AK165" s="4">
         <v>52</v>
@@ -22511,16 +22579,16 @@
     </row>
     <row r="166" ht="13.5" customHeight="1">
       <c r="A166" s="2">
-        <v>19927</v>
+        <v>19928</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D166" s="4">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c t="s" r="E166" s="4">
         <v>254</v>
@@ -22551,68 +22619,66 @@
         <v>52</v>
       </c>
       <c r="O166" s="5">
-        <v>9253.6499999999996</v>
+        <v>23860.779999999999</v>
       </c>
       <c r="P166" s="5">
-        <v>10795.924999999999</v>
+        <v>23860.779999999999</v>
       </c>
       <c r="Q166" s="6">
-        <v>-0.11838849726903522</v>
+        <v>-0.21588771195561274</v>
       </c>
       <c r="R166" s="7">
-        <v>144.66666666666669</v>
+        <v>283</v>
       </c>
       <c r="S166" s="6">
-        <v>-0.1079136690647482</v>
+        <v>-0.20949720670391059</v>
       </c>
       <c r="T166" s="6">
-        <v>0</v>
+        <v>-0.021921831557895427</v>
       </c>
       <c r="U166" s="6">
-        <v>-0.32349397264863056</v>
+        <v>-0.35933703759893854</v>
       </c>
       <c r="V166" s="6">
-        <v>0.17117310466680716</v>
+        <v>0.023457762068130213</v>
       </c>
       <c r="W166" s="6">
-        <v>0.086163405791228331</v>
+        <v>-0.014513335272359078</v>
       </c>
       <c r="X166" s="8">
-        <v>34.57142727272727</v>
+        <v>27.676583000000001</v>
       </c>
       <c r="Y166" s="6">
-        <v>0.63636363636363635</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="Z166" s="6">
-        <v>0.25974025974025972</v>
+        <v>0.125</v>
       </c>
       <c r="AA166" s="8">
-        <v>7.089295934959349</v>
+        <v>4.7725177304964532</v>
       </c>
       <c r="AB166" s="8">
-        <v>10.937938157894738</v>
+        <v>8.3227045918367342</v>
       </c>
       <c r="AC166" s="8">
-        <v>18.262180000000001</v>
+        <v>12.798870000000001</v>
       </c>
       <c r="AD166" s="8">
-        <v>25.036796103896105</v>
+        <v>19.522666999999998</v>
       </c>
       <c r="AE166" s="6">
-        <v>0.38961038961038963</v>
+        <v>0.68999999999999995</v>
       </c>
       <c r="AF166" s="9"/>
       <c r="AG166" s="5">
-        <v>-818.39999999999998</v>
+        <v>-197</v>
       </c>
       <c r="AH166" s="10">
-        <v>1</v>
-      </c>
-      <c r="AI166" s="11">
         <v>4</v>
       </c>
+      <c r="AI166" s="11"/>
       <c r="AJ166" s="12">
-        <v>45984</v>
+        <v>46044</v>
       </c>
       <c t="s" r="AK166" s="4">
         <v>52</v>
@@ -22644,7 +22710,7 @@
     </row>
     <row r="167" ht="13.5" customHeight="1">
       <c r="A167" s="2">
-        <v>19928</v>
+        <v>19930</v>
       </c>
       <c r="B167" s="3">
         <v>0</v>
@@ -22684,66 +22750,66 @@
         <v>52</v>
       </c>
       <c r="O167" s="5">
-        <v>23860.779999999999</v>
+        <v>33698.979999999996</v>
       </c>
       <c r="P167" s="5">
-        <v>23860.779999999999</v>
+        <v>33698.979999999996</v>
       </c>
       <c r="Q167" s="6">
-        <v>-0.28585341617881233</v>
+        <v>0.52382851571897016</v>
       </c>
       <c r="R167" s="7">
-        <v>283</v>
+        <v>428</v>
       </c>
       <c r="S167" s="6">
-        <v>-0.20949720670391059</v>
+        <v>0.083544303797468356</v>
       </c>
       <c r="T167" s="6">
-        <v>-0.021921831557895427</v>
+        <v>0.34008170573708757</v>
       </c>
       <c r="U167" s="6">
-        <v>-0.35933703759893854</v>
+        <v>0.046861554860117421</v>
       </c>
       <c r="V167" s="6">
-        <v>0.023457762068130213</v>
+        <v>0.062499547464047865</v>
       </c>
       <c r="W167" s="6">
-        <v>-0.014513335272359078</v>
+        <v>0.031650839283562889</v>
       </c>
       <c r="X167" s="8">
-        <v>27.676583000000001</v>
+        <v>28.993490304709141</v>
       </c>
       <c r="Y167" s="6">
-        <v>0.59999999999999998</v>
+        <v>0.20221606648199447</v>
       </c>
       <c r="Z167" s="6">
-        <v>0.125</v>
+        <v>0.16066481994459833</v>
       </c>
       <c r="AA167" s="8">
-        <v>4.7725177304964532</v>
+        <v>4.6082560465116273</v>
       </c>
       <c r="AB167" s="8">
-        <v>8.3227045918367342</v>
+        <v>14.80751223880597</v>
       </c>
       <c r="AC167" s="8">
-        <v>12.798870000000001</v>
+        <v>19.274826000000001</v>
       </c>
       <c r="AD167" s="8">
-        <v>19.522666999999998</v>
+        <v>24.790812742382268</v>
       </c>
       <c r="AE167" s="6">
-        <v>0.68999999999999995</v>
+        <v>0.60110803324099726</v>
       </c>
       <c r="AF167" s="9"/>
       <c r="AG167" s="5">
-        <v>-197</v>
+        <v>-138.30000000000001</v>
       </c>
       <c r="AH167" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI167" s="11"/>
       <c r="AJ167" s="12">
-        <v>46044</v>
+        <v>46010</v>
       </c>
       <c t="s" r="AK167" s="4">
         <v>52</v>
@@ -22775,19 +22841,19 @@
     </row>
     <row r="168" ht="13.5" customHeight="1">
       <c r="A168" s="2">
-        <v>19930</v>
+        <v>19931</v>
       </c>
       <c r="B168" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C168" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D168" s="4">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c t="s" r="E168" s="4">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c t="s" r="F168" s="4">
         <v>47</v>
@@ -22815,66 +22881,66 @@
         <v>52</v>
       </c>
       <c r="O168" s="5">
-        <v>26175.639999999999</v>
+        <v>31819.280000000006</v>
       </c>
       <c r="P168" s="5">
-        <v>30538.246666666662</v>
+        <v>31819.280000000006</v>
       </c>
       <c r="Q168" s="6">
-        <v>0.35107748052792664</v>
+        <v>0.0068430169015494258</v>
       </c>
       <c r="R168" s="7">
-        <v>381.5</v>
+        <v>346</v>
       </c>
       <c r="S168" s="6">
-        <v>0.034810126582278667</v>
+        <v>-0.21896162528216701</v>
       </c>
       <c r="T168" s="6">
-        <v>0.34784080924095839</v>
+        <v>0.26625968280866191</v>
       </c>
       <c r="U168" s="6">
-        <v>0.051583678565261443</v>
+        <v>-0.19831493987293239</v>
       </c>
       <c r="V168" s="6">
-        <v>0.067777311271090213</v>
+        <v>0.084911915040189467</v>
       </c>
       <c r="W168" s="6">
-        <v>0.034537627351231906</v>
+        <v>0.059081035145986963</v>
       </c>
       <c r="X168" s="8">
-        <v>28.897810218978101</v>
+        <v>25.096017610062891</v>
       </c>
       <c r="Y168" s="6">
-        <v>0.24452554744525548</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="Z168" s="6">
-        <v>0.17518248175182483</v>
+        <v>0.031446540880503145</v>
       </c>
       <c r="AA168" s="8">
-        <v>4.3657072727272723</v>
+        <v>4.3129950724637682</v>
       </c>
       <c r="AB168" s="8">
-        <v>15.260599599999999</v>
+        <v>5.714300675675676</v>
       </c>
       <c r="AC168" s="8">
-        <v>19.540709</v>
+        <v>10.330812999999999</v>
       </c>
       <c r="AD168" s="8">
-        <v>24.718005109489052</v>
+        <v>16.645283018867925</v>
       </c>
       <c r="AE168" s="6">
-        <v>0.63138686131386856</v>
+        <v>0.8176100628930818</v>
       </c>
       <c r="AF168" s="9"/>
       <c r="AG168" s="5">
-        <v>-138.30000000000001</v>
+        <v>-502.79000000000002</v>
       </c>
       <c r="AH168" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI168" s="11"/>
       <c r="AJ168" s="12">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c t="s" r="AK168" s="4">
         <v>52</v>
@@ -22898,7 +22964,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR168" s="4">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c t="s" r="AS168" s="4">
         <v>56</v>
@@ -22906,19 +22972,19 @@
     </row>
     <row r="169" ht="13.5" customHeight="1">
       <c r="A169" s="2">
-        <v>19931</v>
+        <v>19933</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D169" s="4">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c t="s" r="E169" s="4">
-        <v>126</v>
+        <v>259</v>
       </c>
       <c t="s" r="F169" s="4">
         <v>47</v>
@@ -22946,66 +23012,66 @@
         <v>52</v>
       </c>
       <c r="O169" s="5">
-        <v>24208.450000000004</v>
+        <v>18743.720000000001</v>
       </c>
       <c r="P169" s="5">
-        <v>28243.191666666669</v>
+        <v>18743.720000000001</v>
       </c>
       <c r="Q169" s="6">
-        <v>-0.041523572269632103</v>
+        <v>0.19816641491414755</v>
       </c>
       <c r="R169" s="7">
-        <v>299.83333333333337</v>
+        <v>227</v>
       </c>
       <c r="S169" s="6">
-        <v>-0.21165644171779141</v>
+        <v>0.35928143712574845</v>
       </c>
       <c r="T169" s="6">
-        <v>0.19974946764456211</v>
+        <v>-0.0011815157290015002</v>
       </c>
       <c r="U169" s="6">
-        <v>-0.26317153721118042</v>
+        <v>-0.32700104354951953</v>
       </c>
       <c r="V169" s="6">
-        <v>0.089389056300589256</v>
+        <v>0.071155779108949546</v>
       </c>
       <c r="W169" s="6">
-        <v>0.060870501828906846</v>
+        <v>0.0093094647167157856</v>
       </c>
       <c r="X169" s="8">
-        <v>25.583480701754386</v>
+        <v>18.462244897959181</v>
       </c>
       <c r="Y169" s="6">
-        <v>0.78947368421052633</v>
+        <v>0.93197278911564629</v>
       </c>
       <c r="Z169" s="6">
-        <v>0.043859649122807015</v>
+        <v>0.061224489795918366</v>
       </c>
       <c r="AA169" s="8">
-        <v>4.307942578125</v>
+        <v>4.458551304347826</v>
       </c>
       <c r="AB169" s="8">
-        <v>5.8503192307692311</v>
+        <v>7.2677887640449441</v>
       </c>
       <c r="AC169" s="8">
-        <v>10.513350000000001</v>
+        <v>10.969817000000001</v>
       </c>
       <c r="AD169" s="8">
-        <v>16.661988596491227</v>
+        <v>12.848866666666666</v>
       </c>
       <c r="AE169" s="6">
-        <v>0.79824561403508776</v>
+        <v>0.81632653061224492</v>
       </c>
       <c r="AF169" s="9"/>
       <c r="AG169" s="5">
-        <v>-384.30000000000001</v>
+        <v>-913.20000000000005</v>
       </c>
       <c r="AH169" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI169" s="11"/>
       <c r="AJ169" s="12">
-        <v>46017</v>
+        <v>45939</v>
       </c>
       <c t="s" r="AK169" s="4">
         <v>52</v>
@@ -23037,7 +23103,7 @@
     </row>
     <row r="170" ht="13.5" customHeight="1">
       <c r="A170" s="2">
-        <v>19933</v>
+        <v>19936</v>
       </c>
       <c r="B170" s="3">
         <v>0</v>
@@ -23046,10 +23112,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D170" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="E170" s="4">
-        <v>261</v>
+        <v>71</v>
       </c>
       <c t="s" r="F170" s="4">
         <v>47</v>
@@ -23077,66 +23143,66 @@
         <v>52</v>
       </c>
       <c r="O170" s="5">
-        <v>18743.720000000001</v>
+        <v>14901.049999999999</v>
       </c>
       <c r="P170" s="5">
-        <v>18743.720000000001</v>
+        <v>14901.049999999999</v>
       </c>
       <c r="Q170" s="6">
-        <v>0.098504712552467399</v>
+        <v>-0.48106526659351023</v>
       </c>
       <c r="R170" s="7">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="S170" s="6">
-        <v>0.35928143712574845</v>
+        <v>-0.59079903147699753</v>
       </c>
       <c r="T170" s="6">
-        <v>-0.0011815157290015002</v>
+        <v>0.29870762798594735</v>
       </c>
       <c r="U170" s="6">
-        <v>-0.32700104354951953</v>
+        <v>-0.01167519738541915</v>
       </c>
       <c r="V170" s="6">
-        <v>0.071155779108949546</v>
+        <v>0.030603581626798115</v>
       </c>
       <c r="W170" s="6">
-        <v>0.0093094647167157856</v>
+        <v>-0.020812929290217805</v>
       </c>
       <c r="X170" s="8">
-        <v>18.462244897959181</v>
+        <v>24.313371428571426</v>
       </c>
       <c r="Y170" s="6">
-        <v>0.93197278911564629</v>
+        <v>0.73626373626373631</v>
       </c>
       <c r="Z170" s="6">
-        <v>0.061224489795918366</v>
+        <v>0.02197802197802198</v>
       </c>
       <c r="AA170" s="8">
-        <v>4.458551304347826</v>
+        <v>3.422386390532544</v>
       </c>
       <c r="AB170" s="8">
-        <v>7.2677887640449441</v>
+        <v>9.4972222222222218</v>
       </c>
       <c r="AC170" s="8">
-        <v>10.969817000000001</v>
+        <v>13.110042</v>
       </c>
       <c r="AD170" s="8">
-        <v>12.848866666666666</v>
+        <v>19.928021978021977</v>
       </c>
       <c r="AE170" s="6">
-        <v>0.81632653061224492</v>
+        <v>0.79120879120879117</v>
       </c>
       <c r="AF170" s="9"/>
       <c r="AG170" s="5">
-        <v>-913.20000000000005</v>
+        <v>-369.5</v>
       </c>
       <c r="AH170" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI170" s="11"/>
       <c r="AJ170" s="12">
-        <v>45939</v>
+        <v>45967</v>
       </c>
       <c t="s" r="AK170" s="4">
         <v>52</v>
@@ -23160,7 +23226,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR170" s="4">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c t="s" r="AS170" s="4">
         <v>56</v>
@@ -23168,7 +23234,7 @@
     </row>
     <row r="171" ht="13.5" customHeight="1">
       <c r="A171" s="2">
-        <v>19936</v>
+        <v>19940</v>
       </c>
       <c r="B171" s="3">
         <v>0</v>
@@ -23176,11 +23242,9 @@
       <c t="s" r="C171" s="4">
         <v>44</v>
       </c>
-      <c t="s" r="D171" s="4">
-        <v>70</v>
-      </c>
+      <c r="D171" s="4"/>
       <c t="s" r="E171" s="4">
-        <v>71</v>
+        <v>261</v>
       </c>
       <c t="s" r="F171" s="4">
         <v>47</v>
@@ -23208,66 +23272,68 @@
         <v>52</v>
       </c>
       <c r="O171" s="5">
-        <v>14901.049999999999</v>
+        <v>35161.699999999997</v>
       </c>
       <c r="P171" s="5">
-        <v>14901.049999999999</v>
+        <v>35161.699999999997</v>
       </c>
       <c r="Q171" s="6">
-        <v>-0.52879075356544281</v>
+        <v>-0.044481112565879055</v>
       </c>
       <c r="R171" s="7">
-        <v>169</v>
+        <v>381</v>
       </c>
       <c r="S171" s="6">
-        <v>-0.59079903147699753</v>
+        <v>-0.23030303030303023</v>
       </c>
       <c r="T171" s="6">
-        <v>0.29870762798594735</v>
+        <v>-0.01086022860100621</v>
       </c>
       <c r="U171" s="6">
-        <v>-0.01167519738541915</v>
+        <v>-0.29004809494421491</v>
       </c>
       <c r="V171" s="6">
-        <v>0.030603581626798115</v>
+        <v>0.030271147299476421</v>
       </c>
       <c r="W171" s="6">
-        <v>-0.020812929290217805</v>
+        <v>-0.0097200931695566491</v>
       </c>
       <c r="X171" s="8">
-        <v>24.313371428571426</v>
+        <v>25.875512290502794</v>
       </c>
       <c r="Y171" s="6">
-        <v>0.73626373626373631</v>
+        <v>0.68715083798882681</v>
       </c>
       <c r="Z171" s="6">
-        <v>0.02197802197802198</v>
+        <v>0.033519553072625698</v>
       </c>
       <c r="AA171" s="8">
-        <v>3.422386390532544</v>
+        <v>5.5337937185929649</v>
       </c>
       <c r="AB171" s="8">
-        <v>9.4972222222222218</v>
+        <v>7.069160544217687</v>
       </c>
       <c r="AC171" s="8">
-        <v>13.110042</v>
+        <v>12.535009000000001</v>
       </c>
       <c r="AD171" s="8">
-        <v>19.928021978021977</v>
+        <v>17.392228089887642</v>
       </c>
       <c r="AE171" s="6">
-        <v>0.79120879120879117</v>
+        <v>0.71508379888268159</v>
       </c>
       <c r="AF171" s="9"/>
       <c r="AG171" s="5">
-        <v>-369.5</v>
+        <v>-974.79999999999995</v>
       </c>
       <c r="AH171" s="10">
         <v>2</v>
       </c>
-      <c r="AI171" s="11"/>
+      <c r="AI171" s="11">
+        <v>3</v>
+      </c>
       <c r="AJ171" s="12">
-        <v>45967</v>
+        <v>46008</v>
       </c>
       <c t="s" r="AK171" s="4">
         <v>52</v>
@@ -23291,7 +23357,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR171" s="4">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c t="s" r="AS171" s="4">
         <v>56</v>
@@ -23299,7 +23365,7 @@
     </row>
     <row r="172" ht="13.5" customHeight="1">
       <c r="A172" s="2">
-        <v>19940</v>
+        <v>19943</v>
       </c>
       <c r="B172" s="3">
         <v>0</v>
@@ -23307,9 +23373,11 @@
       <c t="s" r="C172" s="4">
         <v>44</v>
       </c>
-      <c r="D172" s="4"/>
+      <c t="s" r="D172" s="4">
+        <v>80</v>
+      </c>
       <c t="s" r="E172" s="4">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="F172" s="4">
         <v>47</v>
@@ -23337,68 +23405,66 @@
         <v>52</v>
       </c>
       <c r="O172" s="5">
-        <v>35161.699999999997</v>
+        <v>17123.860000000001</v>
       </c>
       <c r="P172" s="5">
-        <v>35161.699999999997</v>
+        <v>17123.860000000001</v>
       </c>
       <c r="Q172" s="6">
-        <v>-0.13433867632602148</v>
+        <v>0.16573775859827111</v>
       </c>
       <c r="R172" s="7">
-        <v>381</v>
+        <v>211</v>
       </c>
       <c r="S172" s="6">
-        <v>-0.23030303030303023</v>
+        <v>-0.02314814814814814</v>
       </c>
       <c r="T172" s="6">
-        <v>-0.01086022860100621</v>
+        <v>0.36592326730071373</v>
       </c>
       <c r="U172" s="6">
-        <v>-0.29004809494421491</v>
+        <v>0.021162214594139406</v>
       </c>
       <c r="V172" s="6">
-        <v>0.030271147299476421</v>
+        <v>0.084387019048275336</v>
       </c>
       <c r="W172" s="6">
-        <v>-0.0097200931695566491</v>
+        <v>0.031936228163509862</v>
       </c>
       <c r="X172" s="8">
-        <v>25.875512290502794</v>
+        <v>23.08739918699187</v>
       </c>
       <c r="Y172" s="6">
-        <v>0.68715083798882681</v>
+        <v>0.78861788617886175</v>
       </c>
       <c r="Z172" s="6">
-        <v>0.033519553072625698</v>
+        <v>0.032520325203252036</v>
       </c>
       <c r="AA172" s="8">
-        <v>5.5337937185929649</v>
+        <v>6.488277511961722</v>
       </c>
       <c r="AB172" s="8">
-        <v>7.069160544217687</v>
+        <v>5.9632516393442625</v>
       </c>
       <c r="AC172" s="8">
-        <v>12.535009000000001</v>
+        <v>11.770839</v>
       </c>
       <c r="AD172" s="8">
-        <v>17.392228089887642</v>
+        <v>18.648508943089432</v>
       </c>
       <c r="AE172" s="6">
-        <v>0.71508379888268159</v>
+        <v>0.85365853658536583</v>
       </c>
       <c r="AF172" s="9"/>
       <c r="AG172" s="5">
-        <v>-974.79999999999995</v>
+        <v>-264.39999999999998</v>
       </c>
       <c r="AH172" s="10">
         <v>2</v>
       </c>
-      <c r="AI172" s="11">
-        <v>3</v>
-      </c>
+      <c r="AI172" s="11"/>
       <c r="AJ172" s="12">
-        <v>46008</v>
+        <v>45937</v>
       </c>
       <c t="s" r="AK172" s="4">
         <v>52</v>
@@ -23422,15 +23488,15 @@
         <v>55</v>
       </c>
       <c t="s" r="AR172" s="4">
-        <v>158</v>
+        <v>263</v>
       </c>
       <c t="s" r="AS172" s="4">
         <v>56</v>
       </c>
     </row>
-    <row r="173" ht="13.5" customHeight="1">
+    <row r="173" ht="24.75" customHeight="1">
       <c r="A173" s="2">
-        <v>19943</v>
+        <v>19944</v>
       </c>
       <c r="B173" s="3">
         <v>0</v>
@@ -23439,7 +23505,7 @@
         <v>44</v>
       </c>
       <c t="s" r="D173" s="4">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c t="s" r="E173" s="4">
         <v>264</v>
@@ -23470,66 +23536,66 @@
         <v>52</v>
       </c>
       <c r="O173" s="5">
-        <v>17123.860000000001</v>
+        <v>45798.149999999994</v>
       </c>
       <c r="P173" s="5">
-        <v>17123.860000000001</v>
+        <v>45798.149999999987</v>
       </c>
       <c r="Q173" s="6">
-        <v>0.07296860206537481</v>
+        <v>0.18958489342784945</v>
       </c>
       <c r="R173" s="7">
-        <v>211</v>
+        <v>539</v>
       </c>
       <c r="S173" s="6">
-        <v>-0.02314814814814814</v>
+        <v>0.056862745098039236</v>
       </c>
       <c r="T173" s="6">
-        <v>0.36592326730071373</v>
+        <v>0.33093211407010981</v>
       </c>
       <c r="U173" s="6">
-        <v>0.021162214594139406</v>
+        <v>0.0091979392180688516</v>
       </c>
       <c r="V173" s="6">
-        <v>0.084387019048275336</v>
+        <v>0.019701483575209917</v>
       </c>
       <c r="W173" s="6">
-        <v>0.031936228163509862</v>
+        <v>-0.00099018191782855852</v>
       </c>
       <c r="X173" s="8">
-        <v>23.08739918699187</v>
+        <v>32.120131179775278</v>
       </c>
       <c r="Y173" s="6">
-        <v>0.78861788617886175</v>
+        <v>0.3595505617977528</v>
       </c>
       <c r="Z173" s="6">
-        <v>0.032520325203252036</v>
+        <v>0.18820224719101122</v>
       </c>
       <c r="AA173" s="8">
-        <v>6.488277511961722</v>
+        <v>8.4123858823529396</v>
       </c>
       <c r="AB173" s="8">
-        <v>5.9632516393442625</v>
+        <v>7.3866103932584268</v>
       </c>
       <c r="AC173" s="8">
-        <v>11.770839</v>
+        <v>15.846207</v>
       </c>
       <c r="AD173" s="8">
-        <v>18.648508943089432</v>
+        <v>22.7688202247191</v>
       </c>
       <c r="AE173" s="6">
-        <v>0.85365853658536583</v>
+        <v>0.4859550561797753</v>
       </c>
       <c r="AF173" s="9"/>
       <c r="AG173" s="5">
-        <v>-264.39999999999998</v>
+        <v>-1287.9000000000001</v>
       </c>
       <c r="AH173" s="10">
         <v>2</v>
       </c>
       <c r="AI173" s="11"/>
       <c r="AJ173" s="12">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c t="s" r="AK173" s="4">
         <v>52</v>
@@ -23559,9 +23625,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" ht="24.75" customHeight="1">
+    <row r="174" ht="13.5" customHeight="1">
       <c r="A174" s="2">
-        <v>19944</v>
+        <v>19945</v>
       </c>
       <c r="B174" s="3">
         <v>0</v>
@@ -23570,10 +23636,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D174" s="4">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c t="s" r="E174" s="4">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="F174" s="4">
         <v>47</v>
@@ -23601,66 +23667,66 @@
         <v>52</v>
       </c>
       <c r="O174" s="5">
-        <v>45798.149999999994</v>
+        <v>29316.110000000001</v>
       </c>
       <c r="P174" s="5">
-        <v>45798.149999999987</v>
+        <v>29316.110000000004</v>
       </c>
       <c r="Q174" s="6">
-        <v>0.073356321585856588</v>
+        <v>1.1857972918463862</v>
       </c>
       <c r="R174" s="7">
-        <v>539</v>
+        <v>345</v>
       </c>
       <c r="S174" s="6">
-        <v>0.056862745098039236</v>
+        <v>0.64285714285714279</v>
       </c>
       <c r="T174" s="6">
-        <v>0.33093211407010981</v>
+        <v>1.3581162030023766</v>
       </c>
       <c r="U174" s="6">
-        <v>0.0091979392180688516</v>
+        <v>1.1090558740569605</v>
       </c>
       <c r="V174" s="6">
-        <v>0.019701483575209917</v>
+        <v>0.033609114578980637</v>
       </c>
       <c r="W174" s="6">
-        <v>-0.00099018191782855852</v>
+        <v>0.0081886205229820732</v>
       </c>
       <c r="X174" s="8">
-        <v>32.120131179775278</v>
+        <v>28.3523421875</v>
       </c>
       <c r="Y174" s="6">
-        <v>0.3595505617977528</v>
+        <v>0.8125</v>
       </c>
       <c r="Z174" s="6">
-        <v>0.18820224719101122</v>
+        <v>0.109375</v>
       </c>
       <c r="AA174" s="8">
-        <v>8.4123858823529396</v>
+        <v>6.3999999999999995</v>
       </c>
       <c r="AB174" s="8">
-        <v>7.3866103932584268</v>
+        <v>7.5106557377049175</v>
       </c>
       <c r="AC174" s="8">
-        <v>15.846207</v>
+        <v>13.703279999999999</v>
       </c>
       <c r="AD174" s="8">
-        <v>22.7688202247191</v>
+        <v>20.083331250000001</v>
       </c>
       <c r="AE174" s="6">
-        <v>0.4859550561797753</v>
+        <v>0.65625</v>
       </c>
       <c r="AF174" s="9"/>
       <c r="AG174" s="5">
-        <v>-1287.9000000000001</v>
+        <v>-3094.3099999999999</v>
       </c>
       <c r="AH174" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI174" s="11"/>
       <c r="AJ174" s="12">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c t="s" r="AK174" s="4">
         <v>52</v>
@@ -23684,7 +23750,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR174" s="4">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="AS174" s="4">
         <v>56</v>
@@ -23692,7 +23758,7 @@
     </row>
     <row r="175" ht="13.5" customHeight="1">
       <c r="A175" s="2">
-        <v>19945</v>
+        <v>19947</v>
       </c>
       <c r="B175" s="3">
         <v>0</v>
@@ -23701,10 +23767,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D175" s="4">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c t="s" r="E175" s="4">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c t="s" r="F175" s="4">
         <v>47</v>
@@ -23732,66 +23798,66 @@
         <v>52</v>
       </c>
       <c r="O175" s="5">
-        <v>29316.110000000001</v>
+        <v>62711.62999999999</v>
       </c>
       <c r="P175" s="5">
-        <v>29316.110000000004</v>
+        <v>62711.62999999999</v>
       </c>
       <c r="Q175" s="6">
-        <v>0.98999237701919029</v>
+        <v>0.10350079210328533</v>
       </c>
       <c r="R175" s="7">
-        <v>345</v>
+        <v>628</v>
       </c>
       <c r="S175" s="6">
-        <v>0.64285714285714279</v>
+        <v>-0.092485549132947931</v>
       </c>
       <c r="T175" s="6">
-        <v>1.3581162030023766</v>
+        <v>0.32482081553294023</v>
       </c>
       <c r="U175" s="6">
-        <v>1.1090558740569605</v>
+        <v>-0.008078361222631272</v>
       </c>
       <c r="V175" s="6">
-        <v>0.033609114578980637</v>
+        <v>0.02261740764831021</v>
       </c>
       <c r="W175" s="6">
-        <v>0.0081886205229820732</v>
+        <v>0.0049506686399316997</v>
       </c>
       <c r="X175" s="8">
-        <v>28.3523421875</v>
+        <v>24.362664907651716</v>
       </c>
       <c r="Y175" s="6">
-        <v>0.8125</v>
+        <v>0.62532981530343013</v>
       </c>
       <c r="Z175" s="6">
-        <v>0.109375</v>
+        <v>0.050131926121372031</v>
       </c>
       <c r="AA175" s="8">
-        <v>6.3999999999999995</v>
+        <v>3.1141432612312814</v>
       </c>
       <c r="AB175" s="8">
-        <v>7.5106557377049175</v>
+        <v>6.8710572580645159</v>
       </c>
       <c r="AC175" s="8">
-        <v>13.703279999999999</v>
+        <v>10.113757</v>
       </c>
       <c r="AD175" s="8">
-        <v>20.083331250000001</v>
+        <v>16.871605026455025</v>
       </c>
       <c r="AE175" s="6">
-        <v>0.65625</v>
+        <v>0.85488126649076512</v>
       </c>
       <c r="AF175" s="9"/>
       <c r="AG175" s="5">
-        <v>-3094.3099999999999</v>
+        <v>-1104.79</v>
       </c>
       <c r="AH175" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI175" s="11"/>
       <c r="AJ175" s="12">
-        <v>45953</v>
+        <v>45972</v>
       </c>
       <c t="s" r="AK175" s="4">
         <v>52</v>
@@ -23815,7 +23881,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR175" s="4">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="AS175" s="4">
         <v>56</v>
@@ -23823,7 +23889,7 @@
     </row>
     <row r="176" ht="13.5" customHeight="1">
       <c r="A176" s="2">
-        <v>19947</v>
+        <v>19948</v>
       </c>
       <c r="B176" s="3">
         <v>0</v>
@@ -23832,10 +23898,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D176" s="4">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c t="s" r="E176" s="4">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c t="s" r="F176" s="4">
         <v>47</v>
@@ -23863,66 +23929,66 @@
         <v>52</v>
       </c>
       <c r="O176" s="5">
-        <v>62711.62999999999</v>
+        <v>13861.77</v>
       </c>
       <c r="P176" s="5">
-        <v>62711.62999999999</v>
+        <v>13861.77</v>
       </c>
       <c r="Q176" s="6">
-        <v>-0.021445408184442516</v>
+        <v>0.1372220376318285</v>
       </c>
       <c r="R176" s="7">
-        <v>628</v>
+        <v>191</v>
       </c>
       <c r="S176" s="6">
-        <v>-0.092485549132947931</v>
+        <v>-0.18723404255319154</v>
       </c>
       <c r="T176" s="6">
-        <v>0.32482081553294023</v>
+        <v>0.32261732087604972</v>
       </c>
       <c r="U176" s="6">
-        <v>-0.008078361222631272</v>
+        <v>0.00093762196314034929</v>
       </c>
       <c r="V176" s="6">
-        <v>0.02261740764831021</v>
+        <v>0.027611300721336451</v>
       </c>
       <c r="W176" s="6">
-        <v>0.0049506686399316997</v>
+        <v>-0.061980432513308183</v>
       </c>
       <c r="X176" s="8">
-        <v>24.362664907651716</v>
+        <v>23.043020512820512</v>
       </c>
       <c r="Y176" s="6">
-        <v>0.62532981530343013</v>
+        <v>0.79487179487179482</v>
       </c>
       <c r="Z176" s="6">
-        <v>0.050131926121372031</v>
+        <v>0.0085470085470085479</v>
       </c>
       <c r="AA176" s="8">
-        <v>3.1141432612312814</v>
+        <v>5.9390374331550797</v>
       </c>
       <c r="AB176" s="8">
-        <v>6.8710572580645159</v>
+        <v>5.1912834862385324</v>
       </c>
       <c r="AC176" s="8">
-        <v>10.113757</v>
+        <v>11.361622000000001</v>
       </c>
       <c r="AD176" s="8">
-        <v>16.871605026455025</v>
+        <v>17.489031623931623</v>
       </c>
       <c r="AE176" s="6">
-        <v>0.85488126649076512</v>
+        <v>0.79487179487179482</v>
       </c>
       <c r="AF176" s="9"/>
       <c r="AG176" s="5">
-        <v>-1104.79</v>
+        <v>-32.899999999999999</v>
       </c>
       <c r="AH176" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI176" s="11"/>
       <c r="AJ176" s="12">
-        <v>45972</v>
+        <v>46066</v>
       </c>
       <c t="s" r="AK176" s="4">
         <v>52</v>
@@ -23954,7 +24020,7 @@
     </row>
     <row r="177" ht="13.5" customHeight="1">
       <c r="A177" s="2">
-        <v>19948</v>
+        <v>19951</v>
       </c>
       <c r="B177" s="3">
         <v>0</v>
@@ -23963,7 +24029,7 @@
         <v>44</v>
       </c>
       <c t="s" r="D177" s="4">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c t="s" r="E177" s="4">
         <v>272</v>
@@ -23994,66 +24060,66 @@
         <v>52</v>
       </c>
       <c r="O177" s="5">
-        <v>13861.77</v>
+        <v>33481.68</v>
       </c>
       <c r="P177" s="5">
-        <v>13861.77</v>
+        <v>33481.68</v>
       </c>
       <c r="Q177" s="6">
-        <v>0.052400738864083918</v>
+        <v>-0.027387204508885654</v>
       </c>
       <c r="R177" s="7">
-        <v>191</v>
+        <v>369</v>
       </c>
       <c r="S177" s="6">
-        <v>-0.18723404255319154</v>
+        <v>-0.1978260869565216</v>
       </c>
       <c r="T177" s="6">
-        <v>0.32261732087604972</v>
+        <v>0.3415101422628733</v>
       </c>
       <c r="U177" s="6">
-        <v>0.00093762196314034929</v>
+        <v>-0.0011046847111614471</v>
       </c>
       <c r="V177" s="6">
-        <v>0.027611300721336451</v>
+        <v>0.022685719474052676</v>
       </c>
       <c r="W177" s="6">
-        <v>-0.061980432513308183</v>
+        <v>-0.0044198499000050176</v>
       </c>
       <c r="X177" s="8">
-        <v>23.043020512820512</v>
+        <v>24.750085641025642</v>
       </c>
       <c r="Y177" s="6">
-        <v>0.79487179487179482</v>
+        <v>0.50769230769230766</v>
       </c>
       <c r="Z177" s="6">
-        <v>0.0085470085470085479</v>
+        <v>0.07179487179487179</v>
       </c>
       <c r="AA177" s="8">
-        <v>5.9390374331550797</v>
+        <v>4.2099074999999999</v>
       </c>
       <c r="AB177" s="8">
-        <v>5.1912834862385324</v>
+        <v>4.9516840425531914</v>
       </c>
       <c r="AC177" s="8">
-        <v>11.361622000000001</v>
+        <v>9.2053200000000004</v>
       </c>
       <c r="AD177" s="8">
-        <v>17.489031623931623</v>
+        <v>15.847521538461539</v>
       </c>
       <c r="AE177" s="6">
-        <v>0.79487179487179482</v>
+        <v>0.7846153846153846</v>
       </c>
       <c r="AF177" s="9"/>
       <c r="AG177" s="5">
-        <v>-32.899999999999999</v>
+        <v>-775.47000000000003</v>
       </c>
       <c r="AH177" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI177" s="11"/>
       <c r="AJ177" s="12">
-        <v>46066</v>
+        <v>45958</v>
       </c>
       <c t="s" r="AK177" s="4">
         <v>52</v>
@@ -24085,16 +24151,16 @@
     </row>
     <row r="178" ht="13.5" customHeight="1">
       <c r="A178" s="2">
-        <v>19951</v>
+        <v>19954</v>
       </c>
       <c r="B178" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C178" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D178" s="4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c t="s" r="E178" s="4">
         <v>274</v>
@@ -24125,66 +24191,66 @@
         <v>52</v>
       </c>
       <c r="O178" s="5">
-        <v>25680.220000000001</v>
+        <v>16477.48</v>
       </c>
       <c r="P178" s="5">
-        <v>29960.256666666668</v>
+        <v>16477.48</v>
       </c>
       <c r="Q178" s="6">
-        <v>-0.12355394465604552</v>
+        <v>0.39442432694773233</v>
       </c>
       <c r="R178" s="7">
-        <v>324.33333333333337</v>
+        <v>200</v>
       </c>
       <c r="S178" s="6">
-        <v>-0.20114942528735624</v>
+        <v>0.092896174863388081</v>
       </c>
       <c r="T178" s="6">
-        <v>0.34957366019449992</v>
+        <v>0.2985246651793842</v>
       </c>
       <c r="U178" s="6">
-        <v>0.0068538548345769617</v>
+        <v>-0.059149566559935141</v>
       </c>
       <c r="V178" s="6">
-        <v>0.024266887121683536</v>
+        <v>0.10385365359266101</v>
       </c>
       <c r="W178" s="6">
-        <v>-0.0059353463482789475</v>
+        <v>0.051956761592185215</v>
       </c>
       <c r="X178" s="8">
-        <v>23.97792837837838</v>
+        <v>27.569218367346938</v>
       </c>
       <c r="Y178" s="6">
-        <v>0.52702702702702697</v>
+        <v>0.66326530612244894</v>
       </c>
       <c r="Z178" s="6">
-        <v>0.033783783783783786</v>
+        <v>0.081632653061224483</v>
       </c>
       <c r="AA178" s="8">
-        <v>4.1282527881040894</v>
+        <v>8.199074242424242</v>
       </c>
       <c r="AB178" s="8">
-        <v>4.6089197183098589</v>
+        <v>3.9957905263157896</v>
       </c>
       <c r="AC178" s="8">
-        <v>8.5858290000000004</v>
+        <v>12.110754</v>
       </c>
       <c r="AD178" s="8">
-        <v>15.186036486486485</v>
+        <v>18.857483673469389</v>
       </c>
       <c r="AE178" s="6">
-        <v>0.79729729729729726</v>
+        <v>0.65306122448979587</v>
       </c>
       <c r="AF178" s="9"/>
       <c r="AG178" s="5">
-        <v>-554.57000000000005</v>
+        <v>-683.5</v>
       </c>
       <c r="AH178" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI178" s="11"/>
       <c r="AJ178" s="12">
-        <v>45958</v>
+        <v>45961</v>
       </c>
       <c t="s" r="AK178" s="4">
         <v>52</v>
@@ -24216,16 +24282,16 @@
     </row>
     <row r="179" ht="13.5" customHeight="1">
       <c r="A179" s="2">
-        <v>19954</v>
+        <v>19956</v>
       </c>
       <c r="B179" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C179" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D179" s="4">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c t="s" r="E179" s="4">
         <v>276</v>
@@ -24256,66 +24322,66 @@
         <v>52</v>
       </c>
       <c r="O179" s="5">
-        <v>11370.15</v>
+        <v>15339.459999999999</v>
       </c>
       <c r="P179" s="5">
-        <v>13265.175000000001</v>
+        <v>15339.460000000001</v>
       </c>
       <c r="Q179" s="6">
-        <v>0.15881225858396442</v>
+        <v>-0.55797744798776128</v>
       </c>
       <c r="R179" s="7">
-        <v>159.83333333333331</v>
+        <v>174</v>
       </c>
       <c r="S179" s="6">
-        <v>-0.06164383561643838</v>
+        <v>-0.55949367088607593</v>
       </c>
       <c r="T179" s="6">
-        <v>0.246817509003839</v>
+        <v>0.27116854830613335</v>
       </c>
       <c r="U179" s="6">
-        <v>-0.096885960167631915</v>
+        <v>-0.036831863703155131</v>
       </c>
       <c r="V179" s="6">
-        <v>0.12211303280959356</v>
+        <v>0.026300404316709977</v>
       </c>
       <c r="W179" s="6">
-        <v>0.057552758758679531</v>
+        <v>0.004854408173429834</v>
       </c>
       <c r="X179" s="8">
-        <v>25.947144285714284</v>
+        <v>27.486458035714286</v>
       </c>
       <c r="Y179" s="6">
-        <v>0.68571428571428572</v>
+        <v>0.7946428571428571</v>
       </c>
       <c r="Z179" s="6">
-        <v>0.042857142857142858</v>
+        <v>0.071428571428571425</v>
       </c>
       <c r="AA179" s="8">
-        <v>6.2411197080291974</v>
+        <v>6.6025339181286551</v>
       </c>
       <c r="AB179" s="8">
-        <v>3.9271164179104479</v>
+        <v>9.0414414414414424</v>
       </c>
       <c r="AC179" s="8">
-        <v>10.48259</v>
+        <v>15.377601</v>
       </c>
       <c r="AD179" s="8">
-        <v>17.151667142857143</v>
+        <v>22.15982142857143</v>
       </c>
       <c r="AE179" s="6">
-        <v>0.75714285714285712</v>
+        <v>0.6517857142857143</v>
       </c>
       <c r="AF179" s="9"/>
       <c r="AG179" s="5">
-        <v>-251.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH179" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI179" s="11"/>
       <c r="AJ179" s="12">
-        <v>45961</v>
+        <v>46027</v>
       </c>
       <c t="s" r="AK179" s="4">
         <v>52</v>
@@ -24347,7 +24413,7 @@
     </row>
     <row r="180" ht="13.5" customHeight="1">
       <c r="A180" s="2">
-        <v>19956</v>
+        <v>19958</v>
       </c>
       <c r="B180" s="3">
         <v>0</v>
@@ -24356,7 +24422,7 @@
         <v>44</v>
       </c>
       <c t="s" r="D180" s="4">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c t="s" r="E180" s="4">
         <v>278</v>
@@ -24387,66 +24453,66 @@
         <v>52</v>
       </c>
       <c r="O180" s="5">
-        <v>15339.459999999999</v>
+        <v>29668.300000000003</v>
       </c>
       <c r="P180" s="5">
-        <v>15339.460000000001</v>
+        <v>29668.300000000007</v>
       </c>
       <c r="Q180" s="6">
-        <v>-0.5756579538856188</v>
+        <v>-0.45817143291277562</v>
       </c>
       <c r="R180" s="7">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="S180" s="6">
-        <v>-0.55949367088607593</v>
+        <v>-0.52330827067669172</v>
       </c>
       <c r="T180" s="6">
-        <v>0.27116854830613335</v>
+        <v>0.39576622185969534</v>
       </c>
       <c r="U180" s="6">
-        <v>-0.036831863703155131</v>
+        <v>0.0582352544635183</v>
       </c>
       <c r="V180" s="6">
-        <v>0.026300404316709977</v>
+        <v>0.028433614329098737</v>
       </c>
       <c r="W180" s="6">
-        <v>0.004854408173429834</v>
+        <v>0.0026579547867589311</v>
       </c>
       <c r="X180" s="8">
-        <v>27.486458035714286</v>
+        <v>30.926815789473682</v>
       </c>
       <c r="Y180" s="6">
-        <v>0.7946428571428571</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="Z180" s="6">
-        <v>0.071428571428571425</v>
+        <v>0.15789473684210525</v>
       </c>
       <c r="AA180" s="8">
-        <v>6.6025339181286551</v>
+        <v>9.2501639344262294</v>
       </c>
       <c r="AB180" s="8">
-        <v>9.0414414414414424</v>
+        <v>6.2201292307692313</v>
       </c>
       <c r="AC180" s="8">
-        <v>15.377601</v>
+        <v>15.835666</v>
       </c>
       <c r="AD180" s="8">
-        <v>22.15982142857143</v>
+        <v>22.350375187969927</v>
       </c>
       <c r="AE180" s="6">
-        <v>0.6517857142857143</v>
+        <v>0.51127819548872178</v>
       </c>
       <c r="AF180" s="9"/>
       <c r="AG180" s="5">
-        <v>0</v>
+        <v>-2526.23</v>
       </c>
       <c r="AH180" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI180" s="11"/>
       <c r="AJ180" s="12">
-        <v>46027</v>
+        <v>45937</v>
       </c>
       <c t="s" r="AK180" s="4">
         <v>52</v>
@@ -24478,7 +24544,7 @@
     </row>
     <row r="181" ht="13.5" customHeight="1">
       <c r="A181" s="2">
-        <v>19958</v>
+        <v>19959</v>
       </c>
       <c r="B181" s="3">
         <v>0</v>
@@ -24487,7 +24553,7 @@
         <v>44</v>
       </c>
       <c t="s" r="D181" s="4">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c t="s" r="E181" s="4">
         <v>280</v>
@@ -24518,66 +24584,62 @@
         <v>52</v>
       </c>
       <c r="O181" s="5">
-        <v>29668.300000000003</v>
+        <v>18808.269999999997</v>
       </c>
       <c r="P181" s="5">
-        <v>29668.300000000007</v>
-      </c>
-      <c r="Q181" s="6">
-        <v>-0.49565322344845397</v>
-      </c>
+        <v>18808.269999999997</v>
+      </c>
+      <c r="Q181" s="6"/>
       <c r="R181" s="7">
-        <v>317</v>
-      </c>
-      <c r="S181" s="6">
-        <v>-0.52330827067669172</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="S181" s="6"/>
       <c r="T181" s="6">
-        <v>0.39576622185969534</v>
+        <v>0.36847112467015836</v>
       </c>
       <c r="U181" s="6">
-        <v>0.0582352544635183</v>
+        <v>0.042976010021123688</v>
       </c>
       <c r="V181" s="6">
-        <v>0.028433614329098737</v>
+        <v>0.038527972003804707</v>
       </c>
       <c r="W181" s="6">
-        <v>0.0026579547867589311</v>
+        <v>-0.00062980274102828165</v>
       </c>
       <c r="X181" s="8">
-        <v>30.926815789473682</v>
+        <v>23.681525301204822</v>
       </c>
       <c r="Y181" s="6">
-        <v>0.52631578947368418</v>
+        <v>0.75903614457831325</v>
       </c>
       <c r="Z181" s="6">
-        <v>0.15789473684210525</v>
+        <v>0.012048192771084338</v>
       </c>
       <c r="AA181" s="8">
-        <v>9.2501639344262294</v>
+        <v>4.9650234741784036</v>
       </c>
       <c r="AB181" s="8">
-        <v>6.2201292307692313</v>
+        <v>3.9670873417721517</v>
       </c>
       <c r="AC181" s="8">
-        <v>15.835666</v>
+        <v>8.8020080000000007</v>
       </c>
       <c r="AD181" s="8">
-        <v>22.350375187969927</v>
+        <v>15.41164578313253</v>
       </c>
       <c r="AE181" s="6">
-        <v>0.51127819548872178</v>
+        <v>0.86746987951807231</v>
       </c>
       <c r="AF181" s="9"/>
       <c r="AG181" s="5">
-        <v>-2526.23</v>
+        <v>-2139.3000000000002</v>
       </c>
       <c r="AH181" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI181" s="11"/>
       <c r="AJ181" s="12">
-        <v>45937</v>
+        <v>46006</v>
       </c>
       <c t="s" r="AK181" s="4">
         <v>52</v>
@@ -24609,7 +24671,7 @@
     </row>
     <row r="182" ht="13.5" customHeight="1">
       <c r="A182" s="2">
-        <v>19959</v>
+        <v>19961</v>
       </c>
       <c r="B182" s="3">
         <v>0</v>
@@ -24618,7 +24680,7 @@
         <v>44</v>
       </c>
       <c t="s" r="D182" s="4">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c t="s" r="E182" s="4">
         <v>282</v>
@@ -24649,62 +24711,62 @@
         <v>52</v>
       </c>
       <c r="O182" s="5">
-        <v>18808.269999999997</v>
+        <v>17378.690000000002</v>
       </c>
       <c r="P182" s="5">
-        <v>18808.269999999997</v>
+        <v>17378.690000000002</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="7">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="S182" s="6"/>
       <c r="T182" s="6">
-        <v>0.36847112467015836</v>
+        <v>0.35119396226067678</v>
       </c>
       <c r="U182" s="6">
-        <v>0.042976010021123688</v>
+        <v>0.012245514477788603</v>
       </c>
       <c r="V182" s="6">
-        <v>0.038527972003804707</v>
+        <v>0.031591880630818546</v>
       </c>
       <c r="W182" s="6">
-        <v>-0.00062980274102828165</v>
+        <v>0.013934047963339009</v>
       </c>
       <c r="X182" s="8">
-        <v>23.681525301204822</v>
+        <v>23.390213761467891</v>
       </c>
       <c r="Y182" s="6">
-        <v>0.75903614457831325</v>
+        <v>0.73394495412844041</v>
       </c>
       <c r="Z182" s="6">
-        <v>0.012048192771084338</v>
+        <v>0.01834862385321101</v>
       </c>
       <c r="AA182" s="8">
-        <v>4.9650234741784036</v>
+        <v>5.237347120418848</v>
       </c>
       <c r="AB182" s="8">
-        <v>3.9670873417721517</v>
+        <v>3.7961046728971963</v>
       </c>
       <c r="AC182" s="8">
-        <v>8.8020080000000007</v>
+        <v>9.3760739999999991</v>
       </c>
       <c r="AD182" s="8">
-        <v>15.41164578313253</v>
+        <v>16.20993853211009</v>
       </c>
       <c r="AE182" s="6">
-        <v>0.86746987951807231</v>
+        <v>0.87155963302752293</v>
       </c>
       <c r="AF182" s="9"/>
       <c r="AG182" s="5">
-        <v>-2139.3000000000002</v>
+        <v>-482.19999999999999</v>
       </c>
       <c r="AH182" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI182" s="11"/>
       <c r="AJ182" s="12">
-        <v>46006</v>
+        <v>45951</v>
       </c>
       <c t="s" r="AK182" s="4">
         <v>52</v>
@@ -24728,7 +24790,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR182" s="4">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c t="s" r="AS182" s="4">
         <v>56</v>
@@ -24736,19 +24798,19 @@
     </row>
     <row r="183" ht="13.5" customHeight="1">
       <c r="A183" s="2">
-        <v>19961</v>
+        <v>19962</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D183" s="4">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c t="s" r="E183" s="4">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="F183" s="4">
         <v>47</v>
@@ -24776,62 +24838,62 @@
         <v>52</v>
       </c>
       <c r="O183" s="5">
-        <v>12866.77</v>
+        <v>22592.27</v>
       </c>
       <c r="P183" s="5">
-        <v>15011.231666666667</v>
+        <v>22592.27</v>
       </c>
       <c r="Q183" s="6"/>
       <c r="R183" s="7">
-        <v>171.5</v>
+        <v>243</v>
       </c>
       <c r="S183" s="6"/>
       <c r="T183" s="6">
-        <v>0.33841908264467302</v>
+        <v>-0.12554987613019852</v>
       </c>
       <c r="U183" s="6">
-        <v>-0.0091576596146507629</v>
+        <v>-0.39515846349215905</v>
       </c>
       <c r="V183" s="6">
-        <v>0.032861743856461255</v>
+        <v>0.043965657280122805</v>
       </c>
       <c r="W183" s="6">
-        <v>0.013257756220092532</v>
+        <v>0.0001524415209272906</v>
       </c>
       <c r="X183" s="8">
-        <v>22.89875</v>
+        <v>31.63373015873016</v>
       </c>
       <c r="Y183" s="6">
-        <v>0.80000000000000004</v>
+        <v>0.62698412698412698</v>
       </c>
       <c r="Z183" s="6">
-        <v>0.012500000000000001</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="AA183" s="8">
-        <v>5.0663167832167835</v>
+        <v>7.6937330578512393</v>
       </c>
       <c r="AB183" s="8">
-        <v>3.6860746835443039</v>
+        <v>8.7032249999999998</v>
       </c>
       <c r="AC183" s="8">
-        <v>8.9641999999999999</v>
+        <v>16.742322000000001</v>
       </c>
       <c r="AD183" s="8">
-        <v>15.84541625</v>
+        <v>23.394709523809524</v>
       </c>
       <c r="AE183" s="6">
-        <v>0.90000000000000002</v>
+        <v>0.50793650793650791</v>
       </c>
       <c r="AF183" s="9"/>
       <c r="AG183" s="5">
-        <v>-279.5</v>
+        <v>-11913.709999999999</v>
       </c>
       <c r="AH183" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI183" s="11"/>
       <c r="AJ183" s="12">
-        <v>45951</v>
+        <v>46093</v>
       </c>
       <c t="s" r="AK183" s="4">
         <v>52</v>
@@ -24855,7 +24917,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR183" s="4">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c t="s" r="AS183" s="4">
         <v>56</v>
@@ -24863,19 +24925,19 @@
     </row>
     <row r="184" ht="13.5" customHeight="1">
       <c r="A184" s="2">
-        <v>19962</v>
+        <v>19963</v>
       </c>
       <c r="B184" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C184" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D184" s="4">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c t="s" r="E184" s="4">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="F184" s="4">
         <v>47</v>
@@ -24903,63 +24965,61 @@
         <v>52</v>
       </c>
       <c r="O184" s="5">
-        <v>17205.049999999999</v>
+        <v>33775.25</v>
       </c>
       <c r="P184" s="5">
-        <v>20072.558333333331</v>
+        <v>33775.25</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="7">
-        <v>224</v>
+        <v>365</v>
       </c>
       <c r="S184" s="6"/>
       <c r="T184" s="6">
-        <v>-0.22243470957654876</v>
+        <v>0.45272255275682638</v>
       </c>
       <c r="U184" s="6">
-        <v>-0.48064320068817001</v>
+        <v>0.075135710320426943</v>
       </c>
       <c r="V184" s="6">
-        <v>0.048702241493050004</v>
+        <v>0.036676960200146561</v>
       </c>
       <c r="W184" s="6">
-        <v>-0.00019386749820546876</v>
+        <v>0.010119643822029444</v>
       </c>
       <c r="X184" s="8">
-        <v>31.699290425531913</v>
+        <v>28.651878403755866</v>
       </c>
       <c r="Y184" s="6">
-        <v>0.68085106382978722</v>
+        <v>0.34741784037558687</v>
       </c>
       <c r="Z184" s="6">
-        <v>0.14893617021276595</v>
+        <v>0.13145539906103287</v>
       </c>
       <c r="AA184" s="8">
-        <v>7.6447649214659688</v>
+        <v>8.9867116216216214</v>
       </c>
       <c r="AB184" s="8">
-        <v>8.3876333333333335</v>
+        <v>6.4908291866028707</v>
       </c>
       <c r="AC184" s="8">
-        <v>16.607966999999999</v>
+        <v>15.312925</v>
       </c>
       <c r="AD184" s="8">
-        <v>23.395922340425532</v>
+        <v>22.260093896713613</v>
       </c>
       <c r="AE184" s="6">
-        <v>0.53191489361702127</v>
+        <v>0.57746478873239437</v>
       </c>
       <c r="AF184" s="9"/>
       <c r="AG184" s="5">
-        <v>-6526.4899999999998</v>
+        <v>-432.5</v>
       </c>
       <c r="AH184" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI184" s="11"/>
-      <c r="AJ184" s="12">
-        <v>46093</v>
-      </c>
+      <c r="AJ184" s="13"/>
       <c t="s" r="AK184" s="4">
         <v>52</v>
       </c>
@@ -24982,7 +25042,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR184" s="4">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c t="s" r="AS184" s="4">
         <v>56</v>
@@ -24990,16 +25050,16 @@
     </row>
     <row r="185" ht="13.5" customHeight="1">
       <c r="A185" s="2">
-        <v>19963</v>
+        <v>19964</v>
       </c>
       <c r="B185" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D185" s="4">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c t="s" r="E185" s="4">
         <v>286</v>
@@ -25029,59 +25089,27 @@
       <c t="s" r="N185" s="4">
         <v>52</v>
       </c>
-      <c r="O185" s="5">
-        <v>33775.25</v>
-      </c>
-      <c r="P185" s="5">
-        <v>33775.25</v>
-      </c>
+      <c r="O185" s="5"/>
+      <c r="P185" s="5"/>
       <c r="Q185" s="6"/>
-      <c r="R185" s="7">
-        <v>365</v>
-      </c>
+      <c r="R185" s="7"/>
       <c r="S185" s="6"/>
-      <c r="T185" s="6">
-        <v>0.45272255275682638</v>
-      </c>
-      <c r="U185" s="6">
-        <v>0.075135710320426943</v>
-      </c>
-      <c r="V185" s="6">
-        <v>0.036676960200146561</v>
-      </c>
-      <c r="W185" s="6">
-        <v>0.010119643822029444</v>
-      </c>
-      <c r="X185" s="8">
-        <v>28.651878403755866</v>
-      </c>
-      <c r="Y185" s="6">
-        <v>0.34741784037558687</v>
-      </c>
-      <c r="Z185" s="6">
-        <v>0.13145539906103287</v>
-      </c>
-      <c r="AA185" s="8">
-        <v>8.9867116216216214</v>
-      </c>
-      <c r="AB185" s="8">
-        <v>6.4908291866028707</v>
-      </c>
-      <c r="AC185" s="8">
-        <v>15.312925</v>
-      </c>
-      <c r="AD185" s="8">
-        <v>22.260093896713613</v>
-      </c>
-      <c r="AE185" s="6">
-        <v>0.57746478873239437</v>
-      </c>
+      <c r="T185" s="6"/>
+      <c r="U185" s="6"/>
+      <c r="V185" s="6"/>
+      <c r="W185" s="6"/>
+      <c r="X185" s="8"/>
+      <c r="Y185" s="6"/>
+      <c r="Z185" s="6"/>
+      <c r="AA185" s="8"/>
+      <c r="AB185" s="8"/>
+      <c r="AC185" s="8"/>
+      <c r="AD185" s="8"/>
+      <c r="AE185" s="6"/>
       <c r="AF185" s="9"/>
-      <c r="AG185" s="5">
-        <v>-432.5</v>
-      </c>
+      <c r="AG185" s="5"/>
       <c r="AH185" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI185" s="11"/>
       <c r="AJ185" s="13"/>
@@ -25115,16 +25143,16 @@
     </row>
     <row r="186" ht="13.5" customHeight="1">
       <c r="A186" s="2">
-        <v>19964</v>
+        <v>19966</v>
       </c>
       <c r="B186" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D186" s="4">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c t="s" r="E186" s="4">
         <v>288</v>
@@ -25154,30 +25182,64 @@
       <c t="s" r="N186" s="4">
         <v>52</v>
       </c>
-      <c r="O186" s="5"/>
-      <c r="P186" s="5"/>
+      <c r="O186" s="5">
+        <v>29950.950000000001</v>
+      </c>
+      <c r="P186" s="5">
+        <v>29950.950000000001</v>
+      </c>
       <c r="Q186" s="6"/>
-      <c r="R186" s="7"/>
+      <c r="R186" s="7">
+        <v>311</v>
+      </c>
       <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
-      <c r="X186" s="8"/>
-      <c r="Y186" s="6"/>
-      <c r="Z186" s="6"/>
-      <c r="AA186" s="8"/>
-      <c r="AB186" s="8"/>
-      <c r="AC186" s="8"/>
-      <c r="AD186" s="8"/>
-      <c r="AE186" s="6"/>
+      <c r="T186" s="6">
+        <v>0.065960729125453449</v>
+      </c>
+      <c r="U186" s="6">
+        <v>-0.22513287558491468</v>
+      </c>
+      <c r="V186" s="6">
+        <v>0.04956866142810161</v>
+      </c>
+      <c r="W186" s="6">
+        <v>0.0043126678786482566</v>
+      </c>
+      <c r="X186" s="8">
+        <v>26.618527441860465</v>
+      </c>
+      <c r="Y186" s="6">
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="Z186" s="6">
+        <v>0.093023255813953487</v>
+      </c>
+      <c r="AA186" s="8">
+        <v>9.136633766233766</v>
+      </c>
+      <c r="AB186" s="8">
+        <v>4.5258211267605635</v>
+      </c>
+      <c r="AC186" s="8">
+        <v>13.539401</v>
+      </c>
+      <c r="AD186" s="8">
+        <v>20.316743925233645</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>0.80930232558139537</v>
+      </c>
       <c r="AF186" s="9"/>
-      <c r="AG186" s="5"/>
+      <c r="AG186" s="5">
+        <v>-458.39999999999998</v>
+      </c>
       <c r="AH186" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI186" s="11"/>
-      <c r="AJ186" s="13"/>
+      <c r="AJ186" s="12">
+        <v>45963</v>
+      </c>
       <c t="s" r="AK186" s="4">
         <v>52</v>
       </c>
@@ -25200,7 +25262,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR186" s="4">
-        <v>289</v>
+        <v>113</v>
       </c>
       <c t="s" r="AS186" s="4">
         <v>56</v>
@@ -25208,19 +25270,19 @@
     </row>
     <row r="187" ht="13.5" customHeight="1">
       <c r="A187" s="2">
-        <v>19966</v>
+        <v>19967</v>
       </c>
       <c r="B187" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
       </c>
       <c t="s" r="D187" s="4">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c t="s" r="E187" s="4">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c t="s" r="F187" s="4">
         <v>47</v>
@@ -25247,64 +25309,30 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5">
-        <v>29950.950000000001</v>
-      </c>
-      <c r="P187" s="5">
-        <v>29950.950000000001</v>
-      </c>
+      <c r="O187" s="5"/>
+      <c r="P187" s="5"/>
       <c r="Q187" s="6"/>
-      <c r="R187" s="7">
-        <v>311</v>
-      </c>
+      <c r="R187" s="7"/>
       <c r="S187" s="6"/>
-      <c r="T187" s="6">
-        <v>0.065960729125453449</v>
-      </c>
-      <c r="U187" s="6">
-        <v>-0.22513287558491468</v>
-      </c>
-      <c r="V187" s="6">
-        <v>0.04956866142810161</v>
-      </c>
-      <c r="W187" s="6">
-        <v>0.0043126678786482566</v>
-      </c>
-      <c r="X187" s="8">
-        <v>26.618527441860465</v>
-      </c>
-      <c r="Y187" s="6">
-        <v>0.62962962962962965</v>
-      </c>
-      <c r="Z187" s="6">
-        <v>0.093023255813953487</v>
-      </c>
-      <c r="AA187" s="8">
-        <v>9.136633766233766</v>
-      </c>
-      <c r="AB187" s="8">
-        <v>4.5258211267605635</v>
-      </c>
-      <c r="AC187" s="8">
-        <v>13.539401</v>
-      </c>
-      <c r="AD187" s="8">
-        <v>20.316743925233645</v>
-      </c>
-      <c r="AE187" s="6">
-        <v>0.80930232558139537</v>
-      </c>
+      <c r="T187" s="6"/>
+      <c r="U187" s="6"/>
+      <c r="V187" s="6"/>
+      <c r="W187" s="6"/>
+      <c r="X187" s="8"/>
+      <c r="Y187" s="6"/>
+      <c r="Z187" s="6"/>
+      <c r="AA187" s="8"/>
+      <c r="AB187" s="8"/>
+      <c r="AC187" s="8"/>
+      <c r="AD187" s="8"/>
+      <c r="AE187" s="6"/>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5">
-        <v>-458.39999999999998</v>
-      </c>
+      <c r="AG187" s="5"/>
       <c r="AH187" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI187" s="11"/>
-      <c r="AJ187" s="12">
-        <v>45963</v>
-      </c>
+      <c r="AJ187" s="13"/>
       <c t="s" r="AK187" s="4">
         <v>52</v>
       </c>
@@ -25333,205 +25361,112 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" ht="13.5" customHeight="1">
-      <c r="A188" s="2">
-        <v>19967</v>
-      </c>
-      <c r="B188" s="3">
-        <v>7</v>
-      </c>
-      <c t="s" r="C188" s="4">
-        <v>44</v>
-      </c>
-      <c t="s" r="D188" s="4">
-        <v>80</v>
-      </c>
-      <c t="s" r="E188" s="4">
+    <row r="188" ht="24.75" customHeight="1">
+      <c t="s" r="A188" s="14">
+        <v>290</v>
+      </c>
+      <c t="s" r="B188" s="14">
         <v>291</v>
       </c>
-      <c t="s" r="F188" s="4">
-        <v>47</v>
-      </c>
-      <c t="s" r="G188" s="4">
-        <v>48</v>
-      </c>
-      <c t="s" r="H188" s="4">
-        <v>49</v>
-      </c>
-      <c t="s" r="I188" s="4">
-        <v>50</v>
-      </c>
-      <c t="s" r="J188" s="4">
-        <v>47</v>
-      </c>
-      <c t="s" r="K188" s="4">
-        <v>51</v>
-      </c>
-      <c t="s" r="L188" s="4">
-        <v>51</v>
-      </c>
-      <c r="M188" s="4"/>
-      <c t="s" r="N188" s="4">
-        <v>52</v>
-      </c>
-      <c r="O188" s="5"/>
-      <c r="P188" s="5"/>
-      <c r="Q188" s="6"/>
-      <c r="R188" s="7"/>
-      <c r="S188" s="6"/>
-      <c r="T188" s="6"/>
-      <c r="U188" s="6"/>
-      <c r="V188" s="6"/>
-      <c r="W188" s="6"/>
-      <c r="X188" s="8"/>
-      <c r="Y188" s="6"/>
-      <c r="Z188" s="6"/>
-      <c r="AA188" s="8"/>
-      <c r="AB188" s="8"/>
-      <c r="AC188" s="8"/>
-      <c r="AD188" s="8"/>
-      <c r="AE188" s="6"/>
-      <c r="AF188" s="9"/>
-      <c r="AG188" s="5"/>
-      <c r="AH188" s="10">
-        <v>4</v>
-      </c>
-      <c r="AI188" s="11"/>
-      <c r="AJ188" s="13"/>
-      <c t="s" r="AK188" s="4">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL188" s="4">
-        <v>52</v>
-      </c>
-      <c r="AM188" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN188" s="2">
-        <v>1</v>
-      </c>
-      <c t="s" r="AO188" s="4">
-        <v>53</v>
-      </c>
-      <c t="s" r="AP188" s="4">
-        <v>54</v>
-      </c>
-      <c t="s" r="AQ188" s="4">
-        <v>55</v>
-      </c>
-      <c t="s" r="AR188" s="4">
-        <v>113</v>
-      </c>
-      <c t="s" r="AS188" s="4">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="189" ht="24.75" customHeight="1">
-      <c t="s" r="A189" s="14">
+      <c r="C188" s="15"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="15"/>
+      <c r="F188" s="15"/>
+      <c r="G188" s="15"/>
+      <c r="H188" s="15"/>
+      <c r="I188" s="15"/>
+      <c r="J188" s="15"/>
+      <c r="K188" s="15"/>
+      <c r="L188" s="15"/>
+      <c r="M188" s="15"/>
+      <c t="s" r="N188" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O188" s="14">
         <v>292</v>
       </c>
-      <c t="s" r="B189" s="14">
+      <c t="s" r="P188" s="14">
         <v>293</v>
       </c>
-      <c r="C189" s="15"/>
-      <c r="D189" s="15"/>
-      <c r="E189" s="15"/>
-      <c r="F189" s="15"/>
-      <c r="G189" s="15"/>
-      <c r="H189" s="15"/>
-      <c r="I189" s="15"/>
-      <c r="J189" s="15"/>
-      <c r="K189" s="15"/>
-      <c r="L189" s="15"/>
-      <c r="M189" s="15"/>
-      <c t="s" r="N189" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O189" s="14">
+      <c t="s" r="Q188" s="14">
         <v>294</v>
       </c>
-      <c t="s" r="P189" s="14">
+      <c t="s" r="R188" s="14">
         <v>295</v>
       </c>
-      <c t="s" r="Q189" s="14">
+      <c t="s" r="S188" s="14">
         <v>296</v>
       </c>
-      <c t="s" r="R189" s="14">
+      <c t="s" r="T188" s="14">
         <v>297</v>
       </c>
-      <c t="s" r="S189" s="14">
+      <c t="s" r="U188" s="14">
         <v>298</v>
       </c>
-      <c t="s" r="T189" s="14">
+      <c t="s" r="V188" s="14">
         <v>299</v>
       </c>
-      <c t="s" r="U189" s="14">
+      <c t="s" r="W188" s="14">
         <v>300</v>
       </c>
-      <c t="s" r="V189" s="14">
+      <c t="s" r="X188" s="14">
         <v>301</v>
       </c>
-      <c t="s" r="W189" s="14">
+      <c t="s" r="Y188" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="X189" s="14">
+      <c t="s" r="Z188" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Y189" s="14">
+      <c t="s" r="AA188" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="Z189" s="14">
+      <c t="s" r="AB188" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="AA189" s="14">
+      <c t="s" r="AC188" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="AB189" s="14">
+      <c t="s" r="AD188" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="AC189" s="14">
+      <c t="s" r="AE188" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="AD189" s="14">
+      <c r="AF188" s="14"/>
+      <c t="s" r="AG188" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="AE189" s="14">
+      <c t="s" r="AH188" s="14">
         <v>310</v>
       </c>
-      <c r="AF189" s="14"/>
-      <c t="s" r="AG189" s="14">
+      <c t="s" r="AI188" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="AH189" s="14">
+      <c r="AJ188" s="15"/>
+      <c t="s" r="AK188" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL188" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM188" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="AI189" s="14">
-        <v>313</v>
-      </c>
-      <c r="AJ189" s="15"/>
-      <c t="s" r="AK189" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL189" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM189" s="14">
-        <v>314</v>
-      </c>
-      <c t="s" r="AN189" s="14">
-        <v>314</v>
-      </c>
-      <c r="AO189" s="15"/>
-      <c r="AP189" s="15"/>
-      <c r="AQ189" s="15"/>
-      <c r="AR189" s="15"/>
-      <c r="AS189" s="15"/>
+      <c t="s" r="AN188" s="14">
+        <v>312</v>
+      </c>
+      <c r="AO188" s="15"/>
+      <c r="AP188" s="15"/>
+      <c r="AQ188" s="15"/>
+      <c r="AR188" s="15"/>
+      <c r="AS188" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS189" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS188" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>